--- a/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
+++ b/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="924">
   <si>
     <t>Id</t>
   </si>
@@ -76,9 +76,6 @@
     <t>garabet</t>
   </si>
   <si>
-    <t>muvaffakiyet</t>
-  </si>
-  <si>
     <t>yeis</t>
   </si>
   <si>
@@ -106,21 +103,6 @@
     <t>mütemadiyen</t>
   </si>
   <si>
-    <t>“Gönül gözüyle görmek.”</t>
-  </si>
-  <si>
-    <t>Bir şeyi sadece akılla değil, kalp ve sezgiyle kavramak; derin bir anlayışla bakmak</t>
-  </si>
-  <si>
-    <t>“Gerçek güzelliği fark etmek için bakmak yetmez, insanın gönül gözüyle görmeyi öğrenmesi gerekir.”</t>
-  </si>
-  <si>
-    <t>Drahtı ger sarmış ise karınca. Zarar var mı karıncayı kırınca? Yarın hakkın divanına varınca. Süleyman'dan hakkın alır karınca.</t>
-  </si>
-  <si>
-    <t>Kanuni Sultan Süleyman-Muhibbi</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -316,15 +298,9 @@
     <t>taltif</t>
   </si>
   <si>
-    <t>vuzuh</t>
-  </si>
-  <si>
     <t>güzide</t>
   </si>
   <si>
-    <t>hilkat</t>
-  </si>
-  <si>
     <t>mahir</t>
   </si>
   <si>
@@ -358,9 +334,6 @@
     <t>hodbin</t>
   </si>
   <si>
-    <t>havadis</t>
-  </si>
-  <si>
     <t>mütevellit</t>
   </si>
   <si>
@@ -382,27 +355,15 @@
     <t>sukutuhayal</t>
   </si>
   <si>
-    <t>menzil</t>
-  </si>
-  <si>
-    <t>fail</t>
-  </si>
-  <si>
     <t>meçhul</t>
   </si>
   <si>
     <t>mahcup</t>
   </si>
   <si>
-    <t>taammüden</t>
-  </si>
-  <si>
     <t>nakil</t>
   </si>
   <si>
-    <t>zira</t>
-  </si>
-  <si>
     <t>mazi</t>
   </si>
   <si>
@@ -439,9 +400,6 @@
     <t>girift</t>
   </si>
   <si>
-    <t>feriştah</t>
-  </si>
-  <si>
     <t>sirayet</t>
   </si>
   <si>
@@ -454,9 +412,6 @@
     <t>mutabık</t>
   </si>
   <si>
-    <t>meymenet</t>
-  </si>
-  <si>
     <t>velhasıl</t>
   </si>
   <si>
@@ -680,29 +635,6 @@
     </r>
   </si>
   <si>
-    <t>Başarı, başarılı olma durumu.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Çalışkanlığı sayesinde büyük bir </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>muvaffakiyet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> kazandı.</t>
-    </r>
-  </si>
-  <si>
     <t>Umutsuzluk, ümitsizlik, karamsarlık.</t>
   </si>
   <si>
@@ -1082,9 +1014,6 @@
     <t>Bir düşünceye, inanca veya geleneğe körü körüne bağlanma; fanatiklik, bağnazlık.</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Yaşadığı acı olaydan derinden </t>
     </r>
@@ -2336,33 +2265,4309 @@
   </si>
   <si>
     <t>İç karartıcı, sıkıcı, bunaltıcı, hüzün veren.</t>
+  </si>
+  <si>
+    <t>Ödüllendirme, onurlandırma, takdir etme, iyilikle karşılık verme.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Başarılı öğrenciler, müdür tarafından </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>taltif edildi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>müspet</t>
+  </si>
+  <si>
+    <t>Olumlu, iyi, yapıcı, pozitif, faydalı.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Olaylara her zaman </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>müspet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> yönden bakmaya çalışır.</t>
+    </r>
+  </si>
+  <si>
+    <t>Seçkin, değerli, kıymetli, özenle seçilmiş.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Okulumuzun en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>güzide</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> öğrencilerinden biriydi.</t>
+    </r>
+  </si>
+  <si>
+    <t>fıtrat</t>
+  </si>
+  <si>
+    <t>Yaradılış, doğuştan gelen özellik, insanın doğasında var olan nitelik.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Doğaya zarar vermek, insanın </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>fıtratına</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> aykırıdır.</t>
+    </r>
+  </si>
+  <si>
+    <t>Usta, becerikli, yetenekli, bir işi iyi yapan kişi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tamir işlerinde ne kadar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>mahir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> olduğunu herkes bilir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kendi hakkından, çıkarından veya isteğinden gönüllü olarak vazgeçme.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O, kendi mutluluğundan </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>feragat ederek</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> başkalarının huzurunu sağladı.</t>
+    </r>
+  </si>
+  <si>
+    <t>İnceleme, araştırma, ayrıntılı olarak gözden geçirme.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Doktor, hastanın tahlil sonuçlarını </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>tetkik</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> etti.</t>
+    </r>
+  </si>
+  <si>
+    <t>İş bilen, becerikli, çalışkan kimse.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O, oldukça </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>işgüzar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir tüccardır; her işi ustalıkla halleder.</t>
+    </r>
+  </si>
+  <si>
+    <t>Boş söz, gereksiz konuşma, anlamsız lakırdı.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onun söyledikleri tamamen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>lafügüzaf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, hiçbirinin aslı yok.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bir şeyi herkesin görebileceği biçimde ortaya koyma, sergileme.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mağaza, yeni ürünlerini vitrinlerde </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>teşhir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> etti.</t>
+    </r>
+  </si>
+  <si>
+    <t>Karşılaştırma, kıyaslama, benzerlik ve farkları inceleme</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Geçmişle bugünü </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>mukayese</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> etmeden geleceğe yön çizilemez.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yalanlama, doğru olmadığını açıklama, bir iddiayı reddetme.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hakkında çıkan söylentileri </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>tekzip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> etmek zorunda kaldı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Saygı gösterme, hürmet etme, yüceltme.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Büyüklerine karşı </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>tazim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> göstermek, edebin gereğidir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bilgi, bilgiler, öğrenilmiş şeyler.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Seyahatle ilgili tüm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>malumatı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> dosyada bulabilirsiniz.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bencil, kendini beğenmiş, yalnızca kendi çıkarını düşünen kimse.</t>
+  </si>
+  <si>
+    <r>
+      <t>Hodbin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> insanlar, dünyayı sadece kendi aynalarından görürler.</t>
+    </r>
+  </si>
+  <si>
+    <t>yadırgamak</t>
+  </si>
+  <si>
+    <t>Garip bulmak, alışılmadık görmek, tuhaf karşılamak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Artık kimsenin yardım etmemesine şaşırmıyor, hatta </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yadırgamıyorum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bile.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kaynaklanan, doğan, meydana gelen, -den ötürü.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Havanın soğuk olmasından </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>mütevellit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> dışarı çıkamadık.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuhaflık, gariplik, alışılmadık veya anlamsız olma durumu.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Konuşmasındaki </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>garabet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, dinleyenleri hayrete düşürdü.</t>
+    </r>
+  </si>
+  <si>
+    <t>Aksine, tam tersine, ters olarak, bilâkis.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yorgun değildim, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>bilakis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> enerji doluydum.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bir kişiyi veya şeyi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>suçtan, hatadan veya ayıptan uzak tutmak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> anlamına gelir.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu böyle bir davranıştan </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>tenzih</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> ederim, çünkü iyi biridir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tekrar ortaya çıkmak, yeniden baş göstermek, geri dönmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aralarındaki eski tartışmalar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>nüksetmeye</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> başladı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Üzücü, acı veren, kederli, hüzün dolu.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eski bir şarkının sözlerinde </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>hazin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir hatıra gizliydi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gösterişli, görkemli, parlak, göz alıcı.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Düğünleri son derece </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>şaşaalı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir şekilde yapıldı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kendini övmek, kibirlenmek, başkalarına üstünlük taslamak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Malıyla mülküyle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>böbürlenen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> insanlardan hoşlanmam.</t>
+    </r>
+  </si>
+  <si>
+    <t>Beklentinin boşa çıkması, hayal kırıklığı.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uzun süredir beklediği sonuç gelmeyince </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>sukûtuhayale uğradı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>minnet</t>
+  </si>
+  <si>
+    <t>Yapılan bir iyiliğe karşı duyulan gönül borcu, teşekkür duygusu.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bana yaptığı yardımı asla unutmadım, ona derin bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>minnet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> duyuyorum.</t>
+    </r>
+  </si>
+  <si>
+    <t>talim</t>
+  </si>
+  <si>
+    <t>Öğretme, öğretim, eğitim, alıştırma yaptırma.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Çocuklara güzel ahlakı </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>talim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> etmek gerekir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bilinmeyen, tanınmayan, kim olduğu veya ne olduğu belli olmayan.</t>
+  </si>
+  <si>
+    <t>Meçhule gider bir gemi kalkar bu limandan.</t>
+  </si>
+  <si>
+    <t>Bir şeyi kabul etmemek, inkâr etmek, reddetmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onun söylediklerini önce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yadsıdı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, sonra düşündükçe hak verdi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Utanmış, sıkılmış, yüzü kızarmış, çekingen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hatasını anlayınca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>mahcup bir tebessümle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> başını eğdi.</t>
+    </r>
+  </si>
+  <si>
+    <t>ketum</t>
+  </si>
+  <si>
+    <t>Sır saklayan, az konuşan, ağzı sıkı, gizliliğe önem veren.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Devlet işlerinde çalışanların </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ketum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> olması gerekir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kadir : Değer, kıymet ;Şinas : Bilen.Yapılan iyiliğin, emeğin veya değerin kıymetini bilen; vefalı ve takdir edici kimse.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O, dostlarına karşı her zaman </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kadirşinas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir insandı.</t>
+    </r>
+  </si>
+  <si>
+    <t>binaenaleyh</t>
+  </si>
+  <si>
+    <r>
+      <t>“Bu sebeple, bundan dolayı, dolayısıyla, sonuç olarak”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> anlamına gelir.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O çok çalışkandır, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>binaenaleyh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> başarıyı hak ediyor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Geçmiş zaman, geride kalan dönem, eski günler.</t>
+  </si>
+  <si>
+    <r>
+      <t>Mazi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, hatırlanmak için vardır; unutulmak için değil.</t>
+    </r>
+  </si>
+  <si>
+    <t>İncelik, zarafet, kibarlık, başkalarına karşı saygılı ve ölçülü davranma.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bazen bir tebessüm bile büyük bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>nezaket</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> göstergesidir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bağırıp çağırma, feryat figan etme, acı veya üzüntüyle haykırma.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Halk, yıkımın ardından </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>vaveylâ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> içindeydi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kaderin gereği olarak, kaderin bir cilvesiyle, tesadüfen, istemeden.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Biz o akşam </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>hasbelkader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> tanıştık, ama dostluğumuz kalıcı oldu.</t>
+    </r>
+  </si>
+  <si>
+    <t>tevafuk</t>
+  </si>
+  <si>
+    <t>1-Hariç tutulan, dışarıda bırakılan. 2-Eşsiz, nadir, olağanüstü, çok değerli.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O, yeteneğiyle gerçekten </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>müstesna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir sanatçı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Halk arasında kullanılan sade, kaba veya edebi olmayan ifadeler.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Olayı </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>amiyane</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir dille anlatmak gerekirse, herkes kandırıldı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yüce gönüllü, bağışlayıcı, asil, iyi kalpli, cömert kimse.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O, herkese yardım eden </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>alicenap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir insandır.</t>
+    </r>
+  </si>
+  <si>
+    <t>Boşuna, anlamsız, faydasız, bir sonuç vermeyen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu beklemek </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>beyhude</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, artık geri dönmeyecek.</t>
+    </r>
+  </si>
+  <si>
+    <t>Teşekkür eden, minnet duyan, yapılan iyiliğe karşı gönülden memnun olan kişi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">İnsan, kendisine iyilik edenlere karşı </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>müteşekkir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> olmalıdır.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yürekten kopan bir acıyla, içten gelen bir feryatla, çok acılı bir şekilde.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Çocuğun </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>canhıraş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> sesini duyan herkes yardıma koştu.</t>
+    </r>
+  </si>
+  <si>
+    <t>İki kötülükten, iki olumsuz durumdan daha hafif olanı, daha az zararlı olanı.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu karar mükemmel değil ama diğerine göre </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ehvenişer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Karmaşık, içinden çıkılması zor, karışık, birbirine dolanmış.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">İnsan kalbi kadar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>girift</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir labirent yoktur.</t>
+    </r>
+  </si>
+  <si>
+    <t>laubali</t>
+  </si>
+  <si>
+    <t>Ciddiyetten uzak, ölçüsüz biçimde samimi, saygı sınırlarını aşan veya aldırmaz tavırlı kişi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Öğrencilerin öğretmenle bu kadar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>laubali</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> olmaları doğru değil.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bir şeyin (özellikle duygu, hastalık, düşünce veya etki) başka bir yere veya kimseye geçmesi, yayılması.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Toplumdaki huzursuzluk iş yerine de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>sirayet etti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yumuşak başlı, tatlı dilli, uyumlu, insanın içini ısıtan, dostça davranan kimse.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Çocukların arasında </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>münis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir hava vardı; kimse kimseyi incitmiyordu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Zor beğenen, her şeyde kusur bulan, seçici ve titiz kimse.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O kadar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>müşkülpesent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> ki, hiçbir yemeği tam beğenmez.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bir konuda aynı düşüncede olmak, görüş birliği içinde bulunmak, uygun veya örtüşen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Taraflar, anlaşma maddeleri üzerinde </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>mutabık</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> oldular.</t>
+    </r>
+  </si>
+  <si>
+    <t>İki veya daha fazla olayın birbirine denk gelmesi, uyum göstermesi, tesadüf etmesi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ne güzel bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>tevafuk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, tam seni düşünürken aradın.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sonuç olarak, kısacası, özetle söylenecek olursa.</t>
+  </si>
+  <si>
+    <r>
+      <t>Velhasıl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, hayat dediğin şey; bazen ağlatır, bazen güldürür.</t>
+    </r>
+  </si>
+  <si>
+    <t>Asla, katiyen, sakın ha, hiçbir şekilde.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“Kalbini, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>zinhar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> değersiz ellere teslim etme.”</t>
+    </r>
+  </si>
+  <si>
+    <t>Dil; bir milletin konuştuğu, duygu ve düşüncelerini ifade ettiği araç.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Türkçe bizim ana </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>lisanımızdır</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Şeref kazanmış, onur duymuş, değerli bir durumla onurlandırılmış kişi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sizinle tanışmakla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>müşerref oldum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sessiz ve huzurlu olma durumu; gürültü, telaş ve karmaşadan uzaklık.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deniz kenarında bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>sükûnet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> vardı, dalgalar bile usul çarpıyordu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Göz açıp kapayıncaya kadar geçen kısa zaman; an, saniye.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O anı bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>lahza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bile unutamıyorum.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sadakatli, dostlukta ve sevgide bağlı kalan, vefalı kimse.</t>
+  </si>
+  <si>
+    <r>
+      <t>Vefakâr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir eş, hayatın en büyük armağanıdır.</t>
+    </r>
+  </si>
+  <si>
+    <t>Taşıma, bir yerden başka bir yere aktarma</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hastanın şehir dışına </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>nakli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> sabah yapılacak.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bir konuya ilişkin olarak ortaya atılan, kanıtlanmamış ama mantığa dayanan düşünce veya görüş.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onun düşünceleri bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>nazariye</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> olmaktan çıkıp yaşam biçimine dönüştü.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ağzından kaçırmak</t>
+  </si>
+  <si>
+    <t>Gizli kalması gereken bir şeyi istemeden söylemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sürprizi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ağzından kaçırınca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> herkes öğrendi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Aba altından sopa göstermek</t>
+  </si>
+  <si>
+    <t>Dıştan yumuşak görünerek tehdit etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tatlı sözlerle konuşsa da </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>aba altından sopa gösteriyordu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ah u zar etmek</t>
+  </si>
+  <si>
+    <t>Sızlanmak, ağlayıp yakınmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ayrılığın ardından günlerce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ah u zar etti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ak pak olmak</t>
+  </si>
+  <si>
+    <t>Suçsuz, tertemiz olmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mahkeme sonunda onun </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ak pak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> biri olduğu anlaşıldı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Aklı bir karış havada olmak</t>
+  </si>
+  <si>
+    <t>Ciddi olamamak, dikkatsiz ve dalgın davranmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O kadar neşeli ki, sürekli </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>aklı bir karış havada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Arife tarif gerekmez</t>
+  </si>
+  <si>
+    <t>Anlayışlı insana açıklama yapmak gerekmez.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O zaten niyetimi anladı, çünkü </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>arife tarif gerekmez</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ateş almaya gelmek</t>
+  </si>
+  <si>
+    <t>Bir yere çok kısa süreli uğramak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uğraması sadece bir dakikaydı, resmen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ateş almaya geldi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bahtı kara olmak</t>
+  </si>
+  <si>
+    <t>Talihi kötü olmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ne yapsa da yüzü gülmedi, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>bahtı kara</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir kadındı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bıçak kemiğe dayanmak</t>
+  </si>
+  <si>
+    <t>Sabır kalmamak, dayanma sınırına ulaşmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu kadar haksızlıktan sonra artık </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>bıçak kemiğe dayandı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Çanak yalayıcısı olmak</t>
+  </si>
+  <si>
+    <t>Menfaat için güçlü kimselere dalkavukluk etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gerçeği söylemek yerine </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>çanak yalayıcılığı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> tercih etti.</t>
+    </r>
+  </si>
+  <si>
+    <t>dalkavukluk</t>
+  </si>
+  <si>
+    <t>Çam devirmek</t>
+  </si>
+  <si>
+    <t>Uygunsuz bir söz söyleyip kabalık etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sohbetin tam ortasında öyle bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>çam devirdi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> ki herkes sustu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Çetin ceviz</t>
+  </si>
+  <si>
+    <t>Zor başa çıkılan, inatçı kişi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu ikna etmek kolay değil, tam bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>çetin cevizdir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Demir leblebi</t>
+  </si>
+  <si>
+    <t>Kolay yenilmeyen, güçlü, dirayetli kişi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu alt etmek zor; tam bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>demir leblebi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dize gelmek</t>
+  </si>
+  <si>
+    <t>Gururunu bırakıp boyun eğmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onca kibirden sonra sonunda </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>dize geldi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>El etek çekmek</t>
+  </si>
+  <si>
+    <t>İşlerden, insanlardan uzak durmak, kenara çekilmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yıllarca çalıştıktan sonra </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>el etek çekti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>El pençe divan durmak</t>
+  </si>
+  <si>
+    <t>Saygıyla önünde durmak, hizmet etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Padişahın huzuruna çıktıklarında </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>el pençe divan durdular</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Elden ayaktan düşmek</t>
+  </si>
+  <si>
+    <t>Yaşlanmak veya güçten kuvvetten kesilmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eskiden dinçti ama şimdi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>elden ayaktan düştü</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Feleğin çemberinden geçmek</t>
+  </si>
+  <si>
+    <t>Çok tecrübe edinmiş, zorluklar görmüş olmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O kadar olay yaşamış ki, tam anlamıyla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>feleğin çemberinden geçmiş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gam çekmek</t>
+  </si>
+  <si>
+    <t>Üzülmek, dertlenmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elinden geleni yaptı, artık </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>gam çekmesin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gönül koymak</t>
+  </si>
+  <si>
+    <t>Alınmak, gücenmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gelmedi diye hemen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>gönül koymuş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bana.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gözden ırak olmak</t>
+  </si>
+  <si>
+    <t>Uzak kalmak, unutulmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uzun süredir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>gözden ırak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> kaldı ama hâlâ seviliyor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Havanda su dövmek</t>
+  </si>
+  <si>
+    <t>Boşuna çaba harcamak, sonuçsuz iş yapmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onunla tartışmak </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>havanda su dövmek</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> gibiydi.</t>
+    </r>
+  </si>
+  <si>
+    <t>İzine rast gelmek</t>
+  </si>
+  <si>
+    <t>Belirtisini görmek, işaret bulmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kaybolan kervanın hâlâ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>izine rast gelinmedi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kılını kıpırdatmamak</t>
+  </si>
+  <si>
+    <t>Hiç zahmete katlanmamak, ilgisiz kalmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Olan bitene rağmen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kılını kıpırdatmadı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kulağı delik olmak</t>
+  </si>
+  <si>
+    <t>Haberleri herkesten önce duyan kişi olmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O konularda </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kulağı deliktir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, hemen öğrenir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Laf cambazlığı etmek</t>
+  </si>
+  <si>
+    <t>Söz ustalığıyla durumu idare etmeye çalışmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gerçeği gizlemek için </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>laf cambazlığı etti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lafı gediğine koymak</t>
+  </si>
+  <si>
+    <t>Gereken sözü tam yerinde söylemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Herkes susunca o çıktı, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>lafı gediğine koydu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Melül melül bakmak</t>
+  </si>
+  <si>
+    <t>Üzgün, dalgın bir şekilde bakmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Giden geminin ardından </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>melül melül baktı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Nabız yoklamak</t>
+  </si>
+  <si>
+    <t>Birinin düşüncesini, tepkisini ölçmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Patron karar vermeden önce çalışanların </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>nabzını yokladı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Özrü kabahatinden büyük olmak</t>
+  </si>
+  <si>
+    <t>Özrü, yaptığı yanlıştan daha kötü olmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hatasını açıklarken </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>özü kabahatinden büyük</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir mazeret sundu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pabucu dama atılmak</t>
+  </si>
+  <si>
+    <t>Eski değerini yitirmek, yerini başkasına kaptırmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yeni şarkıcı çıkınca eskisinin </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>pabucu dama atıldı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pekmez gibi olmak</t>
+  </si>
+  <si>
+    <t>Fazla yavaş hareket etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu sıcakta herkes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>pekmez gibi oldu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, kimse yerinden kıpırdamıyor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Saman altından su yürütmek</t>
+  </si>
+  <si>
+    <t>Gizlice, fark ettirmeden iş çevirmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O her zamanki gibi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>saman altından su yürütüyordu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sinek avlamak</t>
+  </si>
+  <si>
+    <t>İşlerin durgun olması, kimsenin gelmemesi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kış aylarında bu dükkân hep </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>sinek avlar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ters düşmek</t>
+  </si>
+  <si>
+    <t>Anlaşmazlığa düşmek, aynı fikirde olmamak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu konuda babasıyla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ters düştü</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuz biber olmak</t>
+  </si>
+  <si>
+    <t>Bir olayı daha da kötüleştirmek, artırmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sözleri ortamı yatıştıracağına </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>tuz biber oldu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yan çizmek</t>
+  </si>
+  <si>
+    <t>Sözünden dönmek, kaçınmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">İş zorlaşınca hemen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yan çizdi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yüz çevirmek</t>
+  </si>
+  <si>
+    <t>Birine ilgisini, sevgisini kesmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En yakın dostu ondan </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yüz çevirdi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Zerre kadar şüphesi olmamak</t>
+  </si>
+  <si>
+    <t>Hiç kuşkusu bulunmamak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onun dürüstlüğünden </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>zerre kadar şüphem yok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ayağını denk almak</t>
+  </si>
+  <si>
+    <t>Davranışlarına dikkat etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Müdürün uyarısından sonra herkes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ayağını denk aldı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bağrına taş basmak</t>
+  </si>
+  <si>
+    <t>Acıya katlanmak, sabretmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Olanları unutmak için </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>bağrına taş bastı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Başına iş açmak</t>
+  </si>
+  <si>
+    <t>Kendine veya başkasına sıkıntı doğurmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Düşünmeden yaptığı hareketle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>başına iş açtı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dert yanmak</t>
+  </si>
+  <si>
+    <t>Sıkıntılarını birine anlatmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Arkadaşına içini döküp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>dert yandı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Göz kulak olmak</t>
+  </si>
+  <si>
+    <t>Birini korumak, kollamak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Çocuğa sen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>göz kulak ol</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>, ben birazdan gelirim.</t>
+    </r>
+  </si>
+  <si>
+    <t>Halden anlamak</t>
+  </si>
+  <si>
+    <t>Empati kurmak, birinin durumunu anlayabilmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onun kadar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>halden anlayan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> bir insan görmedim.</t>
+    </r>
+  </si>
+  <si>
+    <t>İçi içine sığmamak</t>
+  </si>
+  <si>
+    <t>Aşırı sevinç veya heyecan duymak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yarını beklerken </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>içi içine sığmıyordu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kula kulluk etmek</t>
+  </si>
+  <si>
+    <t>İnsanlara aşırı boyun eğmek, çıkar için hizmet etmek.</t>
+  </si>
+  <si>
+    <t>Yüreği cız etmek</t>
+  </si>
+  <si>
+    <t>Acıma veya üzüntüyle içinin yanması.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Çocuğun ağladığını görünce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yüreği cız etti.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yüzü tutmamak</t>
+  </si>
+  <si>
+    <t>Birini görmeye, onunla konuşmaya utanmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu görünce yaptığı hatadan dolayı </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yüzü tutmadı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Zembereği boşalmak</t>
+  </si>
+  <si>
+    <t>Birdenbire kendini kaybetmek, sabrı taşmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onca sessizlikten sonra sonunda </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>zembereği boşaldı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Zülfü yare dokunmak</t>
+  </si>
+  <si>
+    <t>Bir kalemde silmek</t>
+  </si>
+  <si>
+    <t>Damarına basmak</t>
+  </si>
+  <si>
+    <t>Kanı kaynamak</t>
+  </si>
+  <si>
+    <t>Nara atmak</t>
+  </si>
+  <si>
+    <t>Üstü kapalı konuşmak</t>
+  </si>
+  <si>
+    <t>Birini bir anda hayatından çıkarmak.</t>
+  </si>
+  <si>
+    <t>Birinin en hassas noktasına dokunmak, kızdırmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu konudan bahsetme, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>damarına basarsın.</t>
+    </r>
+  </si>
+  <si>
+    <t>Birine veya bir şeye aniden sempati duymak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Daha ilk görüşte ona </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kanı kaynadı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yüksek sesle bağırmak, haykırmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Meydanda öfkeyle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>nâra attı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bir şeyi açıkça söylememek, ima etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Konuyu direkt söylemedi, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>üstü kapalı konuştu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Vicdan azabı çekmek</t>
+  </si>
+  <si>
+    <t>Yaptığı bir şeyden dolayı pişmanlık duymak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kırdığı sözler yüzünden yıllarca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>vicdan azabı çekti.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yelkenleri suya indirmek</t>
+  </si>
+  <si>
+    <t>Direnişten vazgeçmek, pes etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tartışmada </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yelkenleri suya indirdi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bir taşla iki kuş vurmak</t>
+  </si>
+  <si>
+    <t>ir hareketle iki iş başarmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu proje ile </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>bir taşla iki kuş vuracağız.</t>
+    </r>
+  </si>
+  <si>
+    <t>İçini kemirmek</t>
+  </si>
+  <si>
+    <t>Bir pişmanlık veya üzüntünün insanı rahatsız etmesi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Söyleyemediği o söz hâlâ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>içini kemiriyor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kalbi pır pır etmek</t>
+  </si>
+  <si>
+    <t>Heyecanlanmak, sevinmek veya korkmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu görünce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kalbi pır pır etti.</t>
+    </r>
+  </si>
+  <si>
+    <t>Köşe bucak kaçmak</t>
+  </si>
+  <si>
+    <t>Birinden ya da bir şeyden sürekli uzak durmak.</t>
+  </si>
+  <si>
+    <t>Onu görmemek için köşe bucak kaçıyor.</t>
+  </si>
+  <si>
+    <t>Laf olsun diye söylemek</t>
+  </si>
+  <si>
+    <t>Gerçek bir anlamı olmadan, gelişigüzel konuşmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O sözleri ciddiye alma, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>laf olsun diye söyledi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Nefes tüketmek</t>
+  </si>
+  <si>
+    <t>Boşuna konuşmak, sonuçsuz çaba harcamak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu ikna etmeye çalışmakla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>nefes tüketiyorsun.</t>
+    </r>
+  </si>
+  <si>
+    <t>Göz pınarları dolmak</t>
+  </si>
+  <si>
+    <t>Ağlamaya başlamak, duygulanmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eski günleri hatırlayınca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>göz pınarları doldu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kulak kabatmak</t>
+  </si>
+  <si>
+    <t>Dikkatlice dinlemek, kulak kesilmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O konuşurken herkes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kulak kabarttı.</t>
+    </r>
+  </si>
+  <si>
+    <t>İçi burkulmak</t>
+  </si>
+  <si>
+    <t>Üzülmek, kalbi sızlamak.</t>
+  </si>
+  <si>
+    <t>Halini öğrenince içim burkuldu.</t>
+  </si>
+  <si>
+    <t>Ağzının tadı kaçmak</t>
+  </si>
+  <si>
+    <t>Keyfi, huzuru bozulmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu kötü haberle herkesin </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ağzının tadı kaçtı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kulağına küpe olmak</t>
+  </si>
+  <si>
+    <t>Bir olaydan ders almak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu yaşadıkların </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kulağına küpe olsun.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bir yastıkta kocamak</t>
+  </si>
+  <si>
+    <t>Evliliği uzun yıllar sürdürmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onlar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>bir yastıkta kocamış</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> örnek bir çiftti.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sözünü esirgememek</t>
+  </si>
+  <si>
+    <t>Doğruyu çekinmeden söylemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Haksızlığı görünce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>sözünü esirgemedi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yüz bulmak</t>
+  </si>
+  <si>
+    <t>Birinin ilgisini görünce daha fazlasını istemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bir kez ilgilenince hemen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yüz buldu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dili tutulmak</t>
+  </si>
+  <si>
+    <t>Şaşkınlıktan konuşamaz hale gelmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O haberi duyunca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>dili tutuldu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Göz ucuyla bakmak</t>
+  </si>
+  <si>
+    <t>Gizlice veya belli etmeden bakmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O da </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>göz ucuyla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> ona baktı ama belli etmedi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kulağını çınlatmak</t>
+  </si>
+  <si>
+    <t>Birini anmak, ondan bahsetmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Az önce senden konuştuk, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kulağın çınlamıştır.</t>
+    </r>
+  </si>
+  <si>
+    <t>İçine kurt düşmek</t>
+  </si>
+  <si>
+    <t>Bir konuda şüpheye kapılmak, endişelenmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Çocuğu geç kalınca annesinin </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>içine kurt düştü.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kalbi yerinden oynamak</t>
+  </si>
+  <si>
+    <t>Çok korkmak ya da heyecanlanmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aniden gelen sesle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kalbi yerinden oynadı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dil dökmek</t>
+  </si>
+  <si>
+    <t>Birini ikna etmek için güzel sözler söylemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Arkadaşını affettirmek için saatlerce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>dil döktü.</t>
+    </r>
+  </si>
+  <si>
+    <t>Göz gezdirmek</t>
+  </si>
+  <si>
+    <t>Kısaca bakmak, hızlıca incelemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ğretmen sınav kâğıtlarına şöyle bir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>göz gezdirdi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Aklıselim davranmak</t>
+  </si>
+  <si>
+    <t>Sakin ve mantıklı hareket etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tartışmalarda </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>aklıselim davranmak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> en doğru yoldur.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sırt çevirmek</t>
+  </si>
+  <si>
+    <t>İlgiyi, dostluğu kesmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eski dostuna neden </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>sırt çevirdin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> kimse anlamadı.</t>
+    </r>
+  </si>
+  <si>
+    <t>El uzatmak</t>
+  </si>
+  <si>
+    <t>Yardım etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Zor zamanında kimse ona </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>el uzatmadı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kendini kaptırmak</t>
+  </si>
+  <si>
+    <t>Bir duyguya, işe ya da düşünceye tamamen dalmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Şarkıya öyle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kendini kaptırdı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> ki etrafı unuttu.</t>
+    </r>
+  </si>
+  <si>
+    <t>İpe un sermek</t>
+  </si>
+  <si>
+    <t>Bir işi yapmamak için bahaneler bulmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yardım edeceğini söyledi ama sonra </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ipe un serdi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Burnundan fitil fitil getirmek</t>
+  </si>
+  <si>
+    <t>Birine yaptığı kötülüğün cezasını ağır biçimde ödetmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onu kandırdığına pişman etti, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>burnundan fitil fitil getirdi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Göbeği çatlamak</t>
+  </si>
+  <si>
+    <t>Çok zorlanmak, büyük emek harcamak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bu evi bitirene kadar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>göbeğimiz çatladı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kalburüstü olmak</t>
+  </si>
+  <si>
+    <t>Seçkin, nitelikli, üstün kişiler arasında yer almak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O, edebiyat dünyasının </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>kalburüstü</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> yazarlarından biridir.</t>
+    </r>
+  </si>
+  <si>
+    <t>Havadan sudan konuşmak</t>
+  </si>
+  <si>
+    <t>Önemsiz, sıradan konular üzerine sohbet etmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Saatlerce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>havadan sudan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> konuştular, ama işe dair tek kelime etmediler.</t>
+    </r>
+  </si>
+  <si>
+    <t>Baş göz etmek</t>
+  </si>
+  <si>
+    <t>Birini evlendirmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kızını sonunda iyi bir delikanlıyla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>baş göz ettiler.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yüz vermemek</t>
+  </si>
+  <si>
+    <t>İlgi göstermemek, önemsememek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ne kadar konuşmak istese de Ayşe ona </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yüz vermedi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Karnından konuşmak</t>
+  </si>
+  <si>
+    <t>Ne dediği anlaşılmayacak kadar alçak sesle konuşmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Söylediklerini duyamadım, yine </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>karnından konuşuyorsun</t>
+    </r>
+  </si>
+  <si>
+    <t>Küplere binmek</t>
+  </si>
+  <si>
+    <t>Aşırı sinirlenmek, öfkeden deliye dönmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O haberi duyunca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>küplere bindi.</t>
+    </r>
+  </si>
+  <si>
+    <t>İçini dökmek</t>
+  </si>
+  <si>
+    <t>Duygu ve düşüncelerini açıkça anlatmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uzun süredir sakladığı her şeyi sonunda </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>içini dökerek</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> anlattı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yüreğine su serpmek</t>
+  </si>
+  <si>
+    <t>Birini rahatlatmak, endişesini gidermek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onun iyi olduğunu duyunca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>yüreğine su serpildi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kılı kırk yarmak</t>
+  </si>
+  <si>
+    <t>En küçük ayrıntıya bile dikkat etmek.</t>
+  </si>
+  <si>
+    <t>Tepesi atmak</t>
+  </si>
+  <si>
+    <t>Çok sinirlenmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sözlerini duyunca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>tepesi attı.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hesap yaparken </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>kılı kırk yarar.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kulağının üstüne yatmak</t>
+  </si>
+  <si>
+    <t>Bilmezden gelmek, ilgilenmemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Konuyu açınca hemen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>kulağının üstüne yattı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Eline yüzüne bulaştırmak</t>
+  </si>
+  <si>
+    <t>Bir işi beceriksizce yapmak.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tamir etmeye çalıştı ama </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>eline yüzüne bulaştırdı.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hatalı olduğunu anlamak.</t>
+  </si>
+  <si>
+    <t>Burnu sürtülmek</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yanıldığını anlayınca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>burnu sürtüldü.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tüy dikmek</t>
+  </si>
+  <si>
+    <t>Bir durumu daha da kötü hâle getirmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Zaten yanlış yapmıştı, bir de o davranışıyla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>tüy dikti.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gönlünden kopmak</t>
+  </si>
+  <si>
+    <t>Karşılıksız bir şey yapmak istemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yardım etmesi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>gönlünden koptu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sineye çekmek</t>
+  </si>
+  <si>
+    <t>Kırıcı bir davranışı kabullenmek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O sözleri bile </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>sineye çekti.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gözü doymaz</t>
+  </si>
+  <si>
+    <t>Açgözlü olmak.</t>
+  </si>
+  <si>
+    <t>Ne versen yetmez, gözü doymaz.</t>
+  </si>
+  <si>
+    <t>Ayağına dolanmak</t>
+  </si>
+  <si>
+    <t>Engellemek.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Her işine biri </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>ayağına dolanıyor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ağzı süt kokmak</t>
+  </si>
+  <si>
+    <t>Deneyimsiz olmak</t>
+  </si>
+  <si>
+    <t>Sen daha ağzı süt kokan bir çocuksun.</t>
+  </si>
+  <si>
+    <t>Avuç açmak</t>
+  </si>
+  <si>
+    <t>Yardım istemek</t>
+  </si>
+  <si>
+    <t>Kimseye avuç açmadan yaşadı.</t>
+  </si>
+  <si>
+    <t>Baş tacı etmek</t>
+  </si>
+  <si>
+    <t>Değer vermek.</t>
+  </si>
+  <si>
+    <t>Türk milleti misafirini baş tacı eder.</t>
+  </si>
+  <si>
+    <t>Bel bağlamak</t>
+  </si>
+  <si>
+    <t>Güvenmek</t>
+  </si>
+  <si>
+    <t>Bu işte ona fazla bel bağlama.</t>
+  </si>
+  <si>
+    <t>Çam sakızı çoban armağanı</t>
+  </si>
+  <si>
+    <t>Değeri küçük ama gönülden gelen hediye.</t>
+  </si>
+  <si>
+    <t>Bu hediyem çam sakızı çoban armağanı.</t>
+  </si>
+  <si>
+    <t>Çorbada tuzu olmak</t>
+  </si>
+  <si>
+    <t>Küçük de olsa katkı sağlamak.</t>
+  </si>
+  <si>
+    <t>Bu projede benim de çorbada tuzum var.</t>
+  </si>
+  <si>
+    <t>Deveyi  hamuduyla yutmak</t>
+  </si>
+  <si>
+    <t>Büyük hırsızlık yapmak.</t>
+  </si>
+  <si>
+    <t>Onlar deveyi hamuduyla yuttular.</t>
+  </si>
+  <si>
+    <t>Eline su dökememek</t>
+  </si>
+  <si>
+    <t>Birine yetişememek.</t>
+  </si>
+  <si>
+    <t>O konuda onun eline kimse su dökemez.</t>
+  </si>
+  <si>
+    <t>Foyası ortaya çıkmak</t>
+  </si>
+  <si>
+    <t>Gerçek yüzü belli olmak.</t>
+  </si>
+  <si>
+    <t>Foyası sonunda ortaya çıktı.</t>
+  </si>
+  <si>
+    <t>Gözünü dört açmak</t>
+  </si>
+  <si>
+    <t>Çok dikkatli olmak</t>
+  </si>
+  <si>
+    <t>Bu işte gözünü dört açman lazım.</t>
+  </si>
+  <si>
+    <t>İncir çekirdeğini doldurmaz</t>
+  </si>
+  <si>
+    <t>Önemsiz şey</t>
+  </si>
+  <si>
+    <t>Kavgaları incir çekirdeğini doldurmaz.</t>
+  </si>
+  <si>
+    <t>İstifini bozmamak</t>
+  </si>
+  <si>
+    <t>Tepkisiz kalmak</t>
+  </si>
+  <si>
+    <t>Olanlara rağmen istifini bozmadı.</t>
+  </si>
+  <si>
+    <t>Kafasına dank etmek</t>
+  </si>
+  <si>
+    <t>Bir şeyi nihayet anlamak.</t>
+  </si>
+  <si>
+    <t>Gerçeği sonunda kafasına dank etti.</t>
+  </si>
+  <si>
+    <t>Ağzından baklayı çıkarmak</t>
+  </si>
+  <si>
+    <t>Sırrını ağzından kaçırmak</t>
+  </si>
+  <si>
+    <t>Nihayet ağzından baklayı çıkardı da her şeyi öğrendik.</t>
+  </si>
+  <si>
+    <t>Ağzı kulaklarına varmak</t>
+  </si>
+  <si>
+    <t>Çok sevinmek</t>
+  </si>
+  <si>
+    <t>Terfi haberini alınca ağzı kulaklarına vardı.</t>
+  </si>
+  <si>
+    <t>Ah almak</t>
+  </si>
+  <si>
+    <t>Birinin bedduasını almak.</t>
+  </si>
+  <si>
+    <t>Kimsenin ahını alma, dönüp dolaşır seni bulur.</t>
+  </si>
+  <si>
+    <t>Aklı bir karış havada</t>
+  </si>
+  <si>
+    <t>Dalgın, hayalperest.</t>
+  </si>
+  <si>
+    <t>Bu aralar aklı bir karış havada geziyor.</t>
+  </si>
+  <si>
+    <t>Al eline sazı</t>
+  </si>
+  <si>
+    <t>Söze başla, anlat bakalım.</t>
+  </si>
+  <si>
+    <t>Hadi bakalım, al eline sazı, dinleyelim seni.</t>
+  </si>
+  <si>
+    <t>Ayağı kesilmek</t>
+  </si>
+  <si>
+    <t>Bir yere artık gitmez olmak.</t>
+  </si>
+  <si>
+    <t>O günden sonra kahveden ayağı kesildi.</t>
+  </si>
+  <si>
+    <t>Azı dişiyle</t>
+  </si>
+  <si>
+    <t>Büyük güçlükle.</t>
+  </si>
+  <si>
+    <t>Bu evi azı dişimle kazandım.</t>
+  </si>
+  <si>
+    <t>Başına çorap örmek</t>
+  </si>
+  <si>
+    <t>Gizlice kötülük planlamak.</t>
+  </si>
+  <si>
+    <t>Onun başına çorap örüyorlarmış.</t>
+  </si>
+  <si>
+    <t>Başına kakmak</t>
+  </si>
+  <si>
+    <t>Bir iyiliği yüzüne vurmak.</t>
+  </si>
+  <si>
+    <t>Yaptığın iyiliği başıma kakma.</t>
+  </si>
+  <si>
+    <t>Canını dişine takmak</t>
+  </si>
+  <si>
+    <t>Büyük gayret göstermek.</t>
+  </si>
+  <si>
+    <t>İşini yetiştirmek için canını dişine taktı.</t>
+  </si>
+  <si>
+    <t>Canına minnet</t>
+  </si>
+  <si>
+    <t>Hoşuna gitmek, sevinmek.</t>
+  </si>
+  <si>
+    <t>Yardım teklifini canına minnet bildi.</t>
+  </si>
+  <si>
+    <t>Çizmeden yukarı çıkmak</t>
+  </si>
+  <si>
+    <t>Haddini aşmak.</t>
+  </si>
+  <si>
+    <t>Memur, amirine laf ederek çizmeden yukarı çıktı.</t>
+  </si>
+  <si>
+    <t>Dağ fare doğurdu</t>
+  </si>
+  <si>
+    <t>Beklenti büyük, sonuç küçük.</t>
+  </si>
+  <si>
+    <t>Onca hazırlıktan sonra dağ fare doğurdu.</t>
+  </si>
+  <si>
+    <t>Kitabın ortasından konuşmak</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bir konuyu </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>doğrudan, açık ve net biçimde</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> söylemek; dolandırmadan, saklamadan, lafı eğip bükmeden konuşmak.</t>
+    </r>
+  </si>
+  <si>
+    <t>Madem dürüst olacağız, kitabın ortasından konuşalım ve gerçeği söyleyelim.</t>
+  </si>
+  <si>
+    <t>Göz boyamak</t>
+  </si>
+  <si>
+    <t>Aldatmak</t>
+  </si>
+  <si>
+    <t>Görünüşte temizlik yaptı, göz boyamak için.</t>
+  </si>
+  <si>
+    <t>Gözü ısırmak</t>
+  </si>
+  <si>
+    <t>Birini daha önce görmüş gibi hissetmek.</t>
+  </si>
+  <si>
+    <t>O adamı bir yerden gözüm ısırıyor ama nereden çıkartamadım.</t>
+  </si>
+  <si>
+    <t>Güme gitmek</t>
+  </si>
+  <si>
+    <t>Boşa gitmek, kaybolmak.</t>
+  </si>
+  <si>
+    <t>Emeklerimiz güme gitmesin, dikkatli olalım.</t>
+  </si>
+  <si>
+    <t>İşi sıkı tutmak</t>
+  </si>
+  <si>
+    <t>Dikkatli ve düzenli çalışmak</t>
+  </si>
+  <si>
+    <t>Dikkatli ve düzenli çalışmak.</t>
+  </si>
+  <si>
+    <t>Kabına sığmamak</t>
+  </si>
+  <si>
+    <t>Coşku, heyecan içinde olmak</t>
+  </si>
+  <si>
+    <t>Mutluluktan kabına sığmıyordu.</t>
+  </si>
+  <si>
+    <t>Kafası dank etmek</t>
+  </si>
+  <si>
+    <t>Geç de olsa gerçeği anlamak.</t>
+  </si>
+  <si>
+    <t>Kafası dank edince hata yaptığını fark etti.</t>
+  </si>
+  <si>
+    <t>Kaş yapayım derken göz çıkarmak</t>
+  </si>
+  <si>
+    <t>İyilik yapayım derken zarara yol açmak.</t>
+  </si>
+  <si>
+    <t>Yardım etmek isterken kaş yapayım derken göz çıkardı.</t>
+  </si>
+  <si>
+    <t>Kendi yağında kavrulmak</t>
+  </si>
+  <si>
+    <t>Kimsenin yardımına muhtaç olmadan geçinmek.</t>
+  </si>
+  <si>
+    <t>Küçük dükkânıyla kendi yağında kavruluyor.</t>
+  </si>
+  <si>
+    <t>Kulak arkası kesilmek</t>
+  </si>
+  <si>
+    <t>Duymazdan gelmek, önemsememek.</t>
+  </si>
+  <si>
+    <t>Söylediklerimi kulak arkası etti.</t>
+  </si>
+  <si>
+    <t>Nabza göre şerbet vermek</t>
+  </si>
+  <si>
+    <t>Duruma uygun davranmak</t>
+  </si>
+  <si>
+    <t>Müdürle konuşurken nabza göre şerbet verir.</t>
+  </si>
+  <si>
+    <t>Kuru gürültü</t>
+  </si>
+  <si>
+    <t>Boş tehdit, etkisiz ses çıkarmak.</t>
+  </si>
+  <si>
+    <t>O sözler kuru gürültüden ibaret.</t>
+  </si>
+  <si>
+    <t>Karıncayı bile incitmemek</t>
+  </si>
+  <si>
+    <t>Çok iyi huylu, kimseye zarar vermeyen.</t>
+  </si>
+  <si>
+    <t>O, karıncayı bile incitmez.</t>
+  </si>
+  <si>
+    <t>İçinden pazarlıklı</t>
+  </si>
+  <si>
+    <t>Kurnaz, çıkarcı kimse</t>
+  </si>
+  <si>
+    <t>O adam içinden pazarlıklıdır, dikkat et.</t>
+  </si>
+  <si>
+    <t>Gözünü budaktan sakınmamak</t>
+  </si>
+  <si>
+    <t>Korkmadan, cesaretle davranmak.</t>
+  </si>
+  <si>
+    <t>Haksızlık karşısında gözünü budaktan sakınmadı.</t>
+  </si>
+  <si>
+    <t>Kulağı kesik olmak</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bir konuda </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>deneyimli, işin inceliklerini bilen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> kimseyi tanımlamak için kullanılır.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bu işi ona bırak, o tam kulağı kesik biridir; yılların tecrübesi var.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Birinin </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>gönlünü incitmek</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>hoşuna gitmeyen bir şey söylemek</t>
+    </r>
+  </si>
+  <si>
+    <t>Şiirinde öyle sözler etmiş ki, zülfü yâre dokunmuş; herkes alınmış.</t>
+  </si>
+  <si>
+    <t>“İnsan, sevdiğini koruduğu kadar insandır.”</t>
+  </si>
+  <si>
+    <t>Cemil Meriç</t>
+  </si>
+  <si>
+    <t>"Kolaylaştırınız! Zorlaştırmayınız! Müjdeleyiniz, nefret ettirmeyiniz!"</t>
+  </si>
+  <si>
+    <t>“Güzel düşün, güzel yaşa.”</t>
+  </si>
+  <si>
+    <t>Şems-i Tebrizi</t>
+  </si>
+  <si>
+    <t>“Bir gönül yıkmak, Kâbe’yi yıkmaktan beterdir.”</t>
+  </si>
+  <si>
+    <t>Yunus Emre</t>
+  </si>
+  <si>
+    <t>“Ya olduğun gibi görün, ya göründüğün gibi ol.”</t>
+  </si>
+  <si>
+    <t>Mevlânâ Celâleddîn-i Rûmî</t>
+  </si>
+  <si>
+    <t>“Kalp ne ile doluysa, dudak ondan konuşur.”</t>
+  </si>
+  <si>
+    <t>“Kendini bilmek, bütün bilgeliklerin başlangıcıdır.”</t>
+  </si>
+  <si>
+    <t>Aristoteles</t>
+  </si>
+  <si>
+    <t>“Sevgi emektir.”</t>
+  </si>
+  <si>
+    <t>Yaşar Kemal</t>
+  </si>
+  <si>
+    <t>“Güçlü olan, kendine hâkim olandır.”</t>
+  </si>
+  <si>
+    <t>Hz. Ali (r.a.)</t>
+  </si>
+  <si>
+    <t>Hz. Ali</t>
+  </si>
+  <si>
+    <t>“İyilik yap, denize at; balık bilmezse Hâlık bilir.”</t>
+  </si>
+  <si>
+    <t>“Bir gün gelir, susmak konuşmaktan daha çok şey anlatır.”</t>
+  </si>
+  <si>
+    <t>Sabahattin Ali</t>
+  </si>
+  <si>
+    <t>“Gerçek dostluk, menfaat bittiğinde belli olur.”</t>
+  </si>
+  <si>
+    <t>“Söz gümüşse, sükût altındır.”</t>
+  </si>
+  <si>
+    <t>Türk Atasözü</t>
+  </si>
+  <si>
+    <t>“Ağaç yaş iken eğilir.”</t>
+  </si>
+  <si>
+    <t>“Gelin tanış olalım; İşi kolay kılalım.Sevelim, sevilelim; dünya kimseye kalmaz.”</t>
+  </si>
+  <si>
+    <t>“Cahile söz, duvara nakış gibidir.”</t>
+  </si>
+  <si>
+    <t>“Sabır acıdır, meyvesi tatlıdır.”</t>
+  </si>
+  <si>
+    <t>“Söz ola kese savaşı, söz ola kestire başı.”</t>
+  </si>
+  <si>
+    <t>“Haksızlık karşısında susan, dilsiz şeytandır.”</t>
+  </si>
+  <si>
+    <t>Hz. Muhammed (sav)</t>
+  </si>
+  <si>
+    <t>Hacı Bektaş-ı Veli</t>
+  </si>
+  <si>
+    <t>“Eline, beline, diline sahip ol.”</t>
+  </si>
+  <si>
+    <t>"Ayinesi(aynası) iştir kişinin lafa bakılmaz/ Şahsın görünür rütbe-i aklı(aklın rütbesi) eserinde."</t>
+  </si>
+  <si>
+    <t>Ziya Paşa</t>
+  </si>
+  <si>
+    <t>Akıl yaşta değil baştadır.”</t>
+  </si>
+  <si>
+    <t>“Yalancının mumu yatsıya kadar yanar.”</t>
+  </si>
+  <si>
+    <t>“Sakınılan göze çöp batar.”</t>
+  </si>
+  <si>
+    <t>“Üzüm üzüme baka baka kararır.”</t>
+  </si>
+  <si>
+    <t>"Hatasız kul olmaz"</t>
+  </si>
+  <si>
+    <t>Orhan Gencebay</t>
+  </si>
+  <si>
+    <t>“Elin ağzı torba değil ki büzesin.”</t>
+  </si>
+  <si>
+    <t>“Her karanlığın sonunda bir sabah vardır.”</t>
+  </si>
+  <si>
+    <t>“Hak yolunda yürüyen yorulmaz.”</t>
+  </si>
+  <si>
+    <t>Söz gümüşse, sükût altındır</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="162"/>
@@ -2372,13 +6577,45 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2393,15 +6630,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2713,9 +6957,9 @@
     <col min="4" max="4" width="64.42578125" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.7109375" customWidth="1"/>
-    <col min="8" max="8" width="41.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="75.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="94.42578125" customWidth="1"/>
+    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" style="1"/>
   </cols>
@@ -2762,35 +7006,35 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>156</v>
+      <c r="C2" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>446</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>447</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>34</v>
+        <v>448</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>909</v>
       </c>
       <c r="J2" s="2">
-        <v>45966</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+        <v>45967</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2798,22 +7042,34 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="F3" t="s">
+        <v>450</v>
+      </c>
+      <c r="G3" t="s">
+        <v>451</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>881</v>
+      </c>
       <c r="J3" s="2">
         <v>45979</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2821,14 +7077,26 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G4" t="s">
+        <v>445</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>884</v>
+      </c>
       <c r="J4" s="2">
         <v>45980</v>
       </c>
@@ -2837,31 +7105,67 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>147</v>
+      </c>
+      <c r="E5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G5" t="s">
+        <v>454</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>886</v>
       </c>
       <c r="J5" s="2">
         <v>45981</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>35</v>
+      <c r="K5" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>149</v>
+      </c>
+      <c r="E6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F6" t="s">
+        <v>456</v>
+      </c>
+      <c r="G6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>887</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="J6" s="2">
         <v>45982</v>
@@ -2871,14 +7175,32 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>151</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F7" t="s">
+        <v>459</v>
+      </c>
+      <c r="G7" t="s">
+        <v>460</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>891</v>
       </c>
       <c r="J7" s="2">
         <v>45985</v>
@@ -2888,14 +7210,32 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>153</v>
+      </c>
+      <c r="E8" t="s">
+        <v>461</v>
+      </c>
+      <c r="F8" t="s">
+        <v>462</v>
+      </c>
+      <c r="G8" t="s">
+        <v>463</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>893</v>
       </c>
       <c r="J8" s="2">
         <v>45986</v>
@@ -2905,14 +7245,32 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>155</v>
+      </c>
+      <c r="E9" t="s">
+        <v>464</v>
+      </c>
+      <c r="F9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G9" t="s">
+        <v>466</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>896</v>
       </c>
       <c r="J9" s="2">
         <v>45987</v>
@@ -2922,14 +7280,32 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>157</v>
+      </c>
+      <c r="E10" t="s">
+        <v>467</v>
+      </c>
+      <c r="F10" t="s">
+        <v>468</v>
+      </c>
+      <c r="G10" t="s">
+        <v>469</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J10" s="2">
         <v>45988</v>
@@ -2939,14 +7315,26 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
       <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" t="s">
-        <v>174</v>
+        <v>473</v>
+      </c>
+      <c r="E11" t="s">
+        <v>470</v>
+      </c>
+      <c r="F11" t="s">
+        <v>471</v>
+      </c>
+      <c r="G11" t="s">
+        <v>472</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>899</v>
       </c>
       <c r="J11" s="2">
         <v>45989</v>
@@ -2956,14 +7344,32 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
-        <v>176</v>
+        <v>159</v>
+      </c>
+      <c r="E12" t="s">
+        <v>474</v>
+      </c>
+      <c r="F12" t="s">
+        <v>475</v>
+      </c>
+      <c r="G12" t="s">
+        <v>476</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>895</v>
       </c>
       <c r="J12" s="2">
         <v>45992</v>
@@ -2973,14 +7379,32 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
+        <v>161</v>
+      </c>
+      <c r="E13" t="s">
+        <v>477</v>
+      </c>
+      <c r="F13" t="s">
+        <v>478</v>
+      </c>
+      <c r="G13" t="s">
+        <v>479</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J13" s="2">
         <v>45993</v>
@@ -2990,14 +7414,32 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>163</v>
+      </c>
+      <c r="E14" t="s">
+        <v>480</v>
+      </c>
+      <c r="F14" t="s">
+        <v>481</v>
+      </c>
+      <c r="G14" t="s">
+        <v>482</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J14" s="2">
         <v>45994</v>
@@ -3007,14 +7449,32 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>165</v>
+      </c>
+      <c r="E15" t="s">
+        <v>483</v>
+      </c>
+      <c r="F15" t="s">
+        <v>484</v>
+      </c>
+      <c r="G15" t="s">
+        <v>485</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>886</v>
       </c>
       <c r="J15" s="2">
         <v>45995</v>
@@ -3024,14 +7484,32 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>167</v>
+      </c>
+      <c r="E16" t="s">
+        <v>486</v>
+      </c>
+      <c r="F16" t="s">
+        <v>487</v>
+      </c>
+      <c r="G16" t="s">
+        <v>488</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J16" s="2">
         <v>45996</v>
@@ -3040,15 +7518,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>169</v>
+      </c>
+      <c r="E17" t="s">
+        <v>489</v>
+      </c>
+      <c r="F17" t="s">
+        <v>490</v>
+      </c>
+      <c r="G17" t="s">
+        <v>491</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>906</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J17" s="2">
         <v>45999</v>
@@ -3057,15 +7553,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>188</v>
+        <v>171</v>
+      </c>
+      <c r="E18" t="s">
+        <v>492</v>
+      </c>
+      <c r="F18" t="s">
+        <v>493</v>
+      </c>
+      <c r="G18" t="s">
+        <v>494</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>886</v>
       </c>
       <c r="J18" s="2">
         <v>46000</v>
@@ -3074,15 +7588,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="D19" t="s">
-        <v>190</v>
+        <v>173</v>
+      </c>
+      <c r="E19" t="s">
+        <v>495</v>
+      </c>
+      <c r="F19" t="s">
+        <v>496</v>
+      </c>
+      <c r="G19" t="s">
+        <v>497</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>909</v>
       </c>
       <c r="J19" s="2">
         <v>46001</v>
@@ -3091,15 +7623,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D20" t="s">
-        <v>192</v>
+        <v>175</v>
+      </c>
+      <c r="E20" t="s">
+        <v>498</v>
+      </c>
+      <c r="F20" t="s">
+        <v>499</v>
+      </c>
+      <c r="G20" t="s">
+        <v>500</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>910</v>
       </c>
       <c r="J20" s="2">
         <v>46002</v>
@@ -3108,15 +7658,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>177</v>
+      </c>
+      <c r="E21" t="s">
+        <v>501</v>
+      </c>
+      <c r="F21" t="s">
+        <v>502</v>
+      </c>
+      <c r="G21" t="s">
+        <v>503</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>913</v>
       </c>
       <c r="J21" s="2">
         <v>46003</v>
@@ -3125,15 +7693,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D22" t="s">
-        <v>196</v>
+        <v>179</v>
+      </c>
+      <c r="E22" t="s">
+        <v>504</v>
+      </c>
+      <c r="F22" t="s">
+        <v>505</v>
+      </c>
+      <c r="G22" t="s">
+        <v>506</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="J22" s="2">
         <v>46006</v>
@@ -3142,15 +7728,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>198</v>
+        <v>181</v>
+      </c>
+      <c r="E23" t="s">
+        <v>507</v>
+      </c>
+      <c r="F23" t="s">
+        <v>508</v>
+      </c>
+      <c r="G23" t="s">
+        <v>509</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J23" s="2">
         <v>46007</v>
@@ -3159,15 +7763,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>183</v>
+      </c>
+      <c r="E24" t="s">
+        <v>510</v>
+      </c>
+      <c r="F24" t="s">
+        <v>511</v>
+      </c>
+      <c r="G24" t="s">
+        <v>512</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J24" s="2">
         <v>46008</v>
@@ -3176,15 +7798,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>185</v>
+      </c>
+      <c r="E25" t="s">
+        <v>513</v>
+      </c>
+      <c r="F25" t="s">
+        <v>514</v>
+      </c>
+      <c r="G25" t="s">
+        <v>515</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>916</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J25" s="2">
         <v>46009</v>
@@ -3193,15 +7833,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
-        <v>204</v>
+        <v>187</v>
+      </c>
+      <c r="E26" t="s">
+        <v>516</v>
+      </c>
+      <c r="F26" t="s">
+        <v>517</v>
+      </c>
+      <c r="G26" t="s">
+        <v>518</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J26" s="2">
         <v>46010</v>
@@ -3210,32 +7868,68 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="D27" t="s">
-        <v>206</v>
+        <v>189</v>
+      </c>
+      <c r="E27" t="s">
+        <v>519</v>
+      </c>
+      <c r="F27" t="s">
+        <v>520</v>
+      </c>
+      <c r="G27" t="s">
+        <v>521</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>919</v>
       </c>
       <c r="J27" s="2">
-        <v>46013</v>
+        <v>45968</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="D28" t="s">
-        <v>208</v>
+        <v>191</v>
+      </c>
+      <c r="E28" t="s">
+        <v>522</v>
+      </c>
+      <c r="F28" t="s">
+        <v>523</v>
+      </c>
+      <c r="G28" t="s">
+        <v>524</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J28" s="2">
         <v>46014</v>
@@ -3244,12 +7938,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>212</v>
+        <v>195</v>
+      </c>
+      <c r="E29" t="s">
+        <v>525</v>
+      </c>
+      <c r="F29" t="s">
+        <v>526</v>
+      </c>
+      <c r="G29" t="s">
+        <v>527</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>902</v>
       </c>
       <c r="J29" s="2">
         <v>46015</v>
@@ -3258,12 +7970,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>211</v>
+        <v>194</v>
+      </c>
+      <c r="E30" t="s">
+        <v>528</v>
+      </c>
+      <c r="F30" t="s">
+        <v>529</v>
+      </c>
+      <c r="G30" t="s">
+        <v>530</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>922</v>
       </c>
       <c r="J30" s="2">
         <v>46016</v>
@@ -3272,15 +7999,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>216</v>
+        <v>198</v>
+      </c>
+      <c r="E31" t="s">
+        <v>531</v>
+      </c>
+      <c r="F31" t="s">
+        <v>532</v>
+      </c>
+      <c r="G31" t="s">
+        <v>533</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>923</v>
       </c>
       <c r="J31" s="2">
         <v>46017</v>
@@ -3289,15 +8031,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
-        <v>218</v>
+        <v>200</v>
+      </c>
+      <c r="E32" t="s">
+        <v>534</v>
+      </c>
+      <c r="F32" t="s">
+        <v>535</v>
+      </c>
+      <c r="G32" t="s">
+        <v>536</v>
       </c>
       <c r="J32" s="2">
         <v>46020</v>
@@ -3306,15 +8060,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D33" t="s">
-        <v>220</v>
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>537</v>
+      </c>
+      <c r="F33" t="s">
+        <v>538</v>
+      </c>
+      <c r="G33" t="s">
+        <v>539</v>
       </c>
       <c r="J33" s="2">
         <v>46021</v>
@@ -3323,15 +8089,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>222</v>
+        <v>204</v>
+      </c>
+      <c r="E34" t="s">
+        <v>540</v>
+      </c>
+      <c r="F34" t="s">
+        <v>541</v>
+      </c>
+      <c r="G34" t="s">
+        <v>542</v>
       </c>
       <c r="J34" s="2">
         <v>46022</v>
@@ -3340,15 +8118,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="D35" t="s">
-        <v>224</v>
+        <v>206</v>
+      </c>
+      <c r="E35" t="s">
+        <v>543</v>
+      </c>
+      <c r="F35" t="s">
+        <v>544</v>
+      </c>
+      <c r="G35" t="s">
+        <v>545</v>
       </c>
       <c r="J35" s="2">
         <v>46024</v>
@@ -3357,15 +8147,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D36" t="s">
-        <v>226</v>
+        <v>208</v>
+      </c>
+      <c r="E36" t="s">
+        <v>546</v>
+      </c>
+      <c r="F36" t="s">
+        <v>547</v>
+      </c>
+      <c r="G36" t="s">
+        <v>548</v>
       </c>
       <c r="J36" s="2">
         <v>46027</v>
@@ -3374,15 +8176,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>228</v>
+        <v>210</v>
+      </c>
+      <c r="E37" t="s">
+        <v>549</v>
+      </c>
+      <c r="F37" t="s">
+        <v>550</v>
+      </c>
+      <c r="G37" t="s">
+        <v>551</v>
       </c>
       <c r="J37" s="2">
         <v>46028</v>
@@ -3391,15 +8205,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="D38" t="s">
-        <v>230</v>
+        <v>212</v>
+      </c>
+      <c r="E38" t="s">
+        <v>552</v>
+      </c>
+      <c r="F38" t="s">
+        <v>553</v>
+      </c>
+      <c r="G38" t="s">
+        <v>554</v>
       </c>
       <c r="J38" s="2">
         <v>46029</v>
@@ -3408,15 +8234,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="D39" t="s">
-        <v>232</v>
+        <v>214</v>
+      </c>
+      <c r="E39" t="s">
+        <v>555</v>
+      </c>
+      <c r="F39" t="s">
+        <v>556</v>
+      </c>
+      <c r="G39" t="s">
+        <v>557</v>
       </c>
       <c r="J39" s="2">
         <v>46030</v>
@@ -3425,15 +8263,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
-        <v>234</v>
+        <v>216</v>
+      </c>
+      <c r="E40" t="s">
+        <v>558</v>
+      </c>
+      <c r="F40" t="s">
+        <v>559</v>
+      </c>
+      <c r="G40" t="s">
+        <v>560</v>
       </c>
       <c r="J40" s="2">
         <v>46031</v>
@@ -3442,15 +8292,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>235</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>236</v>
+        <v>217</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E41" t="s">
+        <v>561</v>
+      </c>
+      <c r="F41" t="s">
+        <v>562</v>
+      </c>
+      <c r="G41" t="s">
+        <v>563</v>
       </c>
       <c r="J41" s="2">
         <v>46034</v>
@@ -3459,15 +8321,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="D42" t="s">
-        <v>238</v>
+        <v>220</v>
+      </c>
+      <c r="E42" t="s">
+        <v>564</v>
+      </c>
+      <c r="F42" t="s">
+        <v>565</v>
+      </c>
+      <c r="G42" t="s">
+        <v>566</v>
       </c>
       <c r="J42" s="2">
         <v>46035</v>
@@ -3476,15 +8350,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="D43" t="s">
-        <v>240</v>
+        <v>222</v>
+      </c>
+      <c r="E43" t="s">
+        <v>567</v>
+      </c>
+      <c r="F43" t="s">
+        <v>568</v>
+      </c>
+      <c r="G43" t="s">
+        <v>569</v>
       </c>
       <c r="J43" s="2">
         <v>46036</v>
@@ -3493,15 +8379,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="D44" t="s">
-        <v>242</v>
+        <v>224</v>
+      </c>
+      <c r="E44" t="s">
+        <v>570</v>
+      </c>
+      <c r="F44" t="s">
+        <v>571</v>
+      </c>
+      <c r="G44" t="s">
+        <v>572</v>
       </c>
       <c r="J44" s="2">
         <v>46037</v>
@@ -3510,15 +8408,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
-        <v>244</v>
+        <v>226</v>
+      </c>
+      <c r="E45" t="s">
+        <v>573</v>
+      </c>
+      <c r="F45" t="s">
+        <v>574</v>
+      </c>
+      <c r="G45" t="s">
+        <v>575</v>
       </c>
       <c r="J45" s="2">
         <v>46038</v>
@@ -3527,15 +8437,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>45</v>
+      </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D46" t="s">
-        <v>246</v>
+        <v>228</v>
+      </c>
+      <c r="E46" t="s">
+        <v>576</v>
+      </c>
+      <c r="F46" t="s">
+        <v>577</v>
+      </c>
+      <c r="G46" t="s">
+        <v>578</v>
       </c>
       <c r="J46" s="2">
         <v>46055</v>
@@ -3544,15 +8466,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>46</v>
+      </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="D47" t="s">
-        <v>248</v>
+        <v>230</v>
+      </c>
+      <c r="E47" t="s">
+        <v>579</v>
+      </c>
+      <c r="F47" t="s">
+        <v>580</v>
+      </c>
+      <c r="G47" t="s">
+        <v>581</v>
       </c>
       <c r="J47" s="2">
         <v>46056</v>
@@ -3561,15 +8495,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>47</v>
+      </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D48" t="s">
-        <v>250</v>
+        <v>232</v>
+      </c>
+      <c r="E48" t="s">
+        <v>584</v>
+      </c>
+      <c r="F48" t="s">
+        <v>585</v>
+      </c>
+      <c r="G48" t="s">
+        <v>586</v>
       </c>
       <c r="J48" s="2">
         <v>46057</v>
@@ -3578,15 +8524,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>48</v>
+      </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>252</v>
+        <v>234</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="F49" t="s">
+        <v>583</v>
       </c>
       <c r="J49" s="2">
         <v>46058</v>
@@ -3595,15 +8550,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>49</v>
+      </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
-        <v>254</v>
+        <v>236</v>
+      </c>
+      <c r="E50" t="s">
+        <v>587</v>
+      </c>
+      <c r="F50" t="s">
+        <v>588</v>
+      </c>
+      <c r="G50" t="s">
+        <v>589</v>
       </c>
       <c r="J50" s="2">
         <v>46059</v>
@@ -3612,15 +8579,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="D51" t="s">
-        <v>256</v>
+        <v>238</v>
+      </c>
+      <c r="E51" t="s">
+        <v>590</v>
+      </c>
+      <c r="F51" t="s">
+        <v>591</v>
+      </c>
+      <c r="G51" t="s">
+        <v>592</v>
       </c>
       <c r="J51" s="2">
         <v>46062</v>
@@ -3629,15 +8608,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>51</v>
+      </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="D52" t="s">
-        <v>258</v>
+        <v>240</v>
+      </c>
+      <c r="E52" t="s">
+        <v>593</v>
+      </c>
+      <c r="F52" t="s">
+        <v>878</v>
+      </c>
+      <c r="G52" t="s">
+        <v>879</v>
       </c>
       <c r="J52" s="2">
         <v>46063</v>
@@ -3646,15 +8637,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>52</v>
+      </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="D53" t="s">
-        <v>260</v>
+        <v>242</v>
+      </c>
+      <c r="E53" t="s">
+        <v>594</v>
+      </c>
+      <c r="F53" t="s">
+        <v>599</v>
+      </c>
+      <c r="G53" t="s">
+        <v>599</v>
       </c>
       <c r="J53" s="2">
         <v>46064</v>
@@ -3663,15 +8666,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D54" t="s">
-        <v>262</v>
+        <v>244</v>
+      </c>
+      <c r="E54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F54" t="s">
+        <v>600</v>
+      </c>
+      <c r="G54" t="s">
+        <v>601</v>
       </c>
       <c r="J54" s="2">
         <v>46065</v>
@@ -3680,15 +8695,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>54</v>
+      </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>246</v>
+      </c>
+      <c r="E55" t="s">
+        <v>596</v>
+      </c>
+      <c r="F55" t="s">
+        <v>602</v>
+      </c>
+      <c r="G55" t="s">
+        <v>603</v>
       </c>
       <c r="J55" s="2">
         <v>46066</v>
@@ -3697,15 +8724,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>55</v>
+      </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="D56" t="s">
-        <v>266</v>
+        <v>248</v>
+      </c>
+      <c r="E56" t="s">
+        <v>597</v>
+      </c>
+      <c r="F56" t="s">
+        <v>604</v>
+      </c>
+      <c r="G56" t="s">
+        <v>605</v>
       </c>
       <c r="J56" s="2">
         <v>46069</v>
@@ -3714,15 +8753,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="D57" t="s">
-        <v>268</v>
+        <v>250</v>
+      </c>
+      <c r="E57" t="s">
+        <v>598</v>
+      </c>
+      <c r="F57" t="s">
+        <v>606</v>
+      </c>
+      <c r="G57" t="s">
+        <v>607</v>
       </c>
       <c r="J57" s="2">
         <v>46070</v>
@@ -3731,15 +8782,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>57</v>
+      </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="D58" t="s">
-        <v>270</v>
+        <v>252</v>
+      </c>
+      <c r="E58" t="s">
+        <v>608</v>
+      </c>
+      <c r="F58" t="s">
+        <v>609</v>
+      </c>
+      <c r="G58" t="s">
+        <v>610</v>
       </c>
       <c r="J58" s="2">
         <v>46071</v>
@@ -3748,15 +8811,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>58</v>
+      </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="D59" t="s">
-        <v>272</v>
+        <v>254</v>
+      </c>
+      <c r="E59" t="s">
+        <v>611</v>
+      </c>
+      <c r="F59" t="s">
+        <v>612</v>
+      </c>
+      <c r="G59" t="s">
+        <v>613</v>
       </c>
       <c r="J59" s="2">
         <v>46072</v>
@@ -3765,15 +8840,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>59</v>
+      </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C60" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="D60" t="s">
-        <v>274</v>
+        <v>256</v>
+      </c>
+      <c r="E60" t="s">
+        <v>614</v>
+      </c>
+      <c r="F60" t="s">
+        <v>615</v>
+      </c>
+      <c r="G60" t="s">
+        <v>616</v>
       </c>
       <c r="J60" s="2">
         <v>46073</v>
@@ -3782,15 +8869,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>60</v>
+      </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="D61" t="s">
-        <v>280</v>
+        <v>262</v>
+      </c>
+      <c r="E61" t="s">
+        <v>617</v>
+      </c>
+      <c r="F61" t="s">
+        <v>618</v>
+      </c>
+      <c r="G61" t="s">
+        <v>619</v>
       </c>
       <c r="J61" s="2">
         <v>46076</v>
@@ -3799,15 +8898,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>61</v>
+      </c>
       <c r="B62" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="C62" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>283</v>
+        <v>265</v>
+      </c>
+      <c r="E62" t="s">
+        <v>620</v>
+      </c>
+      <c r="F62" t="s">
+        <v>621</v>
+      </c>
+      <c r="G62" t="s">
+        <v>622</v>
       </c>
       <c r="J62" s="2">
         <v>46077</v>
@@ -3816,15 +8927,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>62</v>
+      </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C63" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="D63" t="s">
-        <v>285</v>
+        <v>267</v>
+      </c>
+      <c r="E63" t="s">
+        <v>623</v>
+      </c>
+      <c r="F63" t="s">
+        <v>624</v>
+      </c>
+      <c r="G63" t="s">
+        <v>625</v>
       </c>
       <c r="J63" s="2">
         <v>46078</v>
@@ -3833,15 +8956,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>63</v>
+      </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D64" t="s">
-        <v>287</v>
+        <v>269</v>
+      </c>
+      <c r="E64" t="s">
+        <v>626</v>
+      </c>
+      <c r="F64" t="s">
+        <v>627</v>
+      </c>
+      <c r="G64" t="s">
+        <v>628</v>
       </c>
       <c r="J64" s="2">
         <v>46079</v>
@@ -3850,15 +8985,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D65" t="s">
-        <v>289</v>
+        <v>271</v>
+      </c>
+      <c r="E65" t="s">
+        <v>629</v>
+      </c>
+      <c r="F65" t="s">
+        <v>630</v>
+      </c>
+      <c r="G65" t="s">
+        <v>631</v>
       </c>
       <c r="J65" s="2">
         <v>46080</v>
@@ -3867,15 +9014,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
       <c r="B66" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="D66" t="s">
-        <v>291</v>
+        <v>273</v>
+      </c>
+      <c r="E66" t="s">
+        <v>632</v>
+      </c>
+      <c r="F66" t="s">
+        <v>633</v>
+      </c>
+      <c r="G66" t="s">
+        <v>634</v>
       </c>
       <c r="J66" s="2">
         <v>46083</v>
@@ -3884,15 +9043,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>66</v>
+      </c>
       <c r="B67" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="D67" t="s">
-        <v>293</v>
+        <v>275</v>
+      </c>
+      <c r="E67" t="s">
+        <v>635</v>
+      </c>
+      <c r="F67" t="s">
+        <v>636</v>
+      </c>
+      <c r="G67" t="s">
+        <v>637</v>
       </c>
       <c r="J67" s="2">
         <v>46084</v>
@@ -3901,15 +9072,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="D68" t="s">
-        <v>295</v>
+        <v>277</v>
+      </c>
+      <c r="E68" t="s">
+        <v>638</v>
+      </c>
+      <c r="F68" t="s">
+        <v>639</v>
+      </c>
+      <c r="G68" t="s">
+        <v>640</v>
       </c>
       <c r="J68" s="2">
         <v>46085</v>
@@ -3918,15 +9101,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D69" t="s">
-        <v>297</v>
+        <v>279</v>
+      </c>
+      <c r="E69" t="s">
+        <v>641</v>
+      </c>
+      <c r="F69" t="s">
+        <v>642</v>
+      </c>
+      <c r="G69" t="s">
+        <v>643</v>
       </c>
       <c r="J69" s="2">
         <v>46086</v>
@@ -3935,15 +9130,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>69</v>
+      </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D70" t="s">
-        <v>299</v>
+        <v>281</v>
+      </c>
+      <c r="E70" t="s">
+        <v>644</v>
+      </c>
+      <c r="F70" t="s">
+        <v>645</v>
+      </c>
+      <c r="G70" t="s">
+        <v>646</v>
       </c>
       <c r="J70" s="2">
         <v>46087</v>
@@ -3952,15 +9159,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D71" t="s">
-        <v>301</v>
+        <v>283</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="F71" t="s">
+        <v>648</v>
+      </c>
+      <c r="G71" t="s">
+        <v>649</v>
       </c>
       <c r="J71" s="2">
         <v>46090</v>
@@ -3969,15 +9188,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
       <c r="B72" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C72" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D72" t="s">
-        <v>304</v>
+        <v>286</v>
+      </c>
+      <c r="E72" t="s">
+        <v>650</v>
+      </c>
+      <c r="F72" t="s">
+        <v>651</v>
+      </c>
+      <c r="G72" t="s">
+        <v>652</v>
       </c>
       <c r="J72" s="2">
         <v>46091</v>
@@ -3986,15 +9217,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>72</v>
+      </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="D73" t="s">
-        <v>306</v>
+        <v>288</v>
+      </c>
+      <c r="E73" t="s">
+        <v>653</v>
+      </c>
+      <c r="F73" t="s">
+        <v>654</v>
+      </c>
+      <c r="G73" t="s">
+        <v>655</v>
       </c>
       <c r="J73" s="2">
         <v>46092</v>
@@ -4003,15 +9246,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>73</v>
+      </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D74" t="s">
-        <v>210</v>
+        <v>193</v>
+      </c>
+      <c r="E74" t="s">
+        <v>656</v>
+      </c>
+      <c r="F74" t="s">
+        <v>657</v>
+      </c>
+      <c r="G74" t="s">
+        <v>658</v>
       </c>
       <c r="J74" s="2">
         <v>46093</v>
@@ -4020,15 +9275,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>74</v>
+      </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C75" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="D75" t="s">
-        <v>308</v>
+        <v>290</v>
+      </c>
+      <c r="E75" t="s">
+        <v>659</v>
+      </c>
+      <c r="F75" t="s">
+        <v>660</v>
+      </c>
+      <c r="G75" t="s">
+        <v>661</v>
       </c>
       <c r="J75" s="2">
         <v>46094</v>
@@ -4037,15 +9304,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>75</v>
+      </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="D76" t="s">
-        <v>310</v>
+        <v>292</v>
+      </c>
+      <c r="E76" t="s">
+        <v>662</v>
+      </c>
+      <c r="F76" t="s">
+        <v>663</v>
+      </c>
+      <c r="G76" t="s">
+        <v>664</v>
       </c>
       <c r="J76" s="2">
         <v>46097</v>
@@ -4054,15 +9333,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>76</v>
+      </c>
       <c r="B77" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="D77" t="s">
-        <v>312</v>
+        <v>294</v>
+      </c>
+      <c r="E77" t="s">
+        <v>665</v>
+      </c>
+      <c r="F77" t="s">
+        <v>666</v>
+      </c>
+      <c r="G77" t="s">
+        <v>667</v>
       </c>
       <c r="J77" s="2">
         <v>46098</v>
@@ -4071,15 +9362,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>77</v>
+      </c>
       <c r="B78" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="C78" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="D78" t="s">
-        <v>314</v>
+        <v>296</v>
+      </c>
+      <c r="E78" t="s">
+        <v>668</v>
+      </c>
+      <c r="F78" t="s">
+        <v>669</v>
+      </c>
+      <c r="G78" t="s">
+        <v>670</v>
       </c>
       <c r="J78" s="2">
         <v>46099</v>
@@ -4088,15 +9391,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>78</v>
+      </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="D79" t="s">
-        <v>316</v>
+        <v>298</v>
+      </c>
+      <c r="E79" t="s">
+        <v>671</v>
+      </c>
+      <c r="F79" t="s">
+        <v>672</v>
+      </c>
+      <c r="G79" t="s">
+        <v>673</v>
       </c>
       <c r="J79" s="2">
         <v>46100</v>
@@ -4105,15 +9420,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>79</v>
+      </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="D80" t="s">
-        <v>318</v>
+        <v>300</v>
+      </c>
+      <c r="E80" t="s">
+        <v>674</v>
+      </c>
+      <c r="F80" t="s">
+        <v>675</v>
+      </c>
+      <c r="G80" t="s">
+        <v>676</v>
       </c>
       <c r="J80" s="2">
         <v>46101</v>
@@ -4122,15 +9449,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>80</v>
+      </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="D81" t="s">
-        <v>320</v>
+        <v>302</v>
+      </c>
+      <c r="E81" t="s">
+        <v>677</v>
+      </c>
+      <c r="F81" t="s">
+        <v>678</v>
+      </c>
+      <c r="G81" t="s">
+        <v>679</v>
       </c>
       <c r="J81" s="2">
         <v>46104</v>
@@ -4139,15 +9478,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>81</v>
+      </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C82" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D82" t="s">
-        <v>322</v>
+        <v>304</v>
+      </c>
+      <c r="E82" t="s">
+        <v>680</v>
+      </c>
+      <c r="F82" t="s">
+        <v>681</v>
+      </c>
+      <c r="G82" t="s">
+        <v>682</v>
       </c>
       <c r="J82" s="2">
         <v>46105</v>
@@ -4156,15 +9507,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>82</v>
+      </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C83" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="D83" t="s">
-        <v>324</v>
+        <v>306</v>
+      </c>
+      <c r="E83" t="s">
+        <v>683</v>
+      </c>
+      <c r="F83" t="s">
+        <v>684</v>
+      </c>
+      <c r="G83" t="s">
+        <v>685</v>
       </c>
       <c r="J83" s="2">
         <v>46106</v>
@@ -4173,15 +9536,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>83</v>
+      </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C84" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D84" t="s">
-        <v>326</v>
+        <v>308</v>
+      </c>
+      <c r="E84" t="s">
+        <v>686</v>
+      </c>
+      <c r="F84" t="s">
+        <v>687</v>
+      </c>
+      <c r="G84" t="s">
+        <v>688</v>
       </c>
       <c r="J84" s="2">
         <v>46107</v>
@@ -4190,15 +9565,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>84</v>
+      </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C85" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="D85" t="s">
-        <v>328</v>
+        <v>310</v>
+      </c>
+      <c r="E85" t="s">
+        <v>689</v>
+      </c>
+      <c r="F85" t="s">
+        <v>690</v>
+      </c>
+      <c r="G85" t="s">
+        <v>691</v>
       </c>
       <c r="J85" s="2">
         <v>46108</v>
@@ -4207,15 +9594,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>85</v>
+      </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C86" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="D86" t="s">
-        <v>330</v>
+        <v>312</v>
+      </c>
+      <c r="E86" t="s">
+        <v>692</v>
+      </c>
+      <c r="F86" t="s">
+        <v>693</v>
+      </c>
+      <c r="G86" t="s">
+        <v>694</v>
       </c>
       <c r="J86" s="2">
         <v>46111</v>
@@ -4224,12 +9623,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>86</v>
+      </c>
       <c r="B87" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="C87" t="s">
-        <v>331</v>
+        <v>313</v>
+      </c>
+      <c r="E87" t="s">
+        <v>695</v>
+      </c>
+      <c r="F87" t="s">
+        <v>696</v>
+      </c>
+      <c r="G87" t="s">
+        <v>697</v>
       </c>
       <c r="J87" s="2">
         <v>46112</v>
@@ -4238,9 +9649,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>87</v>
+      </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>93</v>
+      </c>
+      <c r="C88" t="s">
+        <v>314</v>
+      </c>
+      <c r="D88" t="s">
+        <v>315</v>
+      </c>
+      <c r="E88" t="s">
+        <v>698</v>
+      </c>
+      <c r="F88" t="s">
+        <v>699</v>
+      </c>
+      <c r="G88" t="s">
+        <v>700</v>
       </c>
       <c r="J88" s="2">
         <v>46113</v>
@@ -4249,9 +9678,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>88</v>
+      </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>316</v>
+      </c>
+      <c r="C89" t="s">
+        <v>317</v>
+      </c>
+      <c r="D89" t="s">
+        <v>318</v>
+      </c>
+      <c r="E89" t="s">
+        <v>701</v>
+      </c>
+      <c r="F89" t="s">
+        <v>702</v>
+      </c>
+      <c r="G89" t="s">
+        <v>703</v>
       </c>
       <c r="J89" s="2">
         <v>46114</v>
@@ -4260,9 +9707,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>89</v>
+      </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="C90" t="s">
+        <v>319</v>
+      </c>
+      <c r="D90" t="s">
+        <v>320</v>
+      </c>
+      <c r="E90" t="s">
+        <v>704</v>
+      </c>
+      <c r="F90" t="s">
+        <v>705</v>
+      </c>
+      <c r="G90" t="s">
+        <v>706</v>
       </c>
       <c r="J90" s="2">
         <v>46115</v>
@@ -4271,9 +9736,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>90</v>
+      </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>321</v>
+      </c>
+      <c r="C91" t="s">
+        <v>322</v>
+      </c>
+      <c r="D91" t="s">
+        <v>323</v>
+      </c>
+      <c r="E91" t="s">
+        <v>707</v>
+      </c>
+      <c r="F91" t="s">
+        <v>708</v>
+      </c>
+      <c r="G91" t="s">
+        <v>709</v>
       </c>
       <c r="J91" s="2">
         <v>46118</v>
@@ -4282,9 +9765,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>91</v>
+      </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>95</v>
+      </c>
+      <c r="C92" t="s">
+        <v>324</v>
+      </c>
+      <c r="D92" t="s">
+        <v>325</v>
+      </c>
+      <c r="E92" t="s">
+        <v>710</v>
+      </c>
+      <c r="F92" t="s">
+        <v>711</v>
+      </c>
+      <c r="G92" t="s">
+        <v>712</v>
       </c>
       <c r="J92" s="2">
         <v>46119</v>
@@ -4293,9 +9794,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>92</v>
+      </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>96</v>
+      </c>
+      <c r="C93" t="s">
+        <v>326</v>
+      </c>
+      <c r="D93" t="s">
+        <v>327</v>
+      </c>
+      <c r="E93" t="s">
+        <v>713</v>
+      </c>
+      <c r="F93" t="s">
+        <v>714</v>
+      </c>
+      <c r="G93" t="s">
+        <v>715</v>
       </c>
       <c r="J93" s="2">
         <v>46120</v>
@@ -4304,9 +9823,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>93</v>
+      </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>97</v>
+      </c>
+      <c r="C94" t="s">
+        <v>328</v>
+      </c>
+      <c r="D94" t="s">
+        <v>329</v>
+      </c>
+      <c r="E94" t="s">
+        <v>716</v>
+      </c>
+      <c r="F94" t="s">
+        <v>717</v>
+      </c>
+      <c r="G94" t="s">
+        <v>718</v>
       </c>
       <c r="J94" s="2">
         <v>46121</v>
@@ -4315,9 +9852,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>94</v>
+      </c>
       <c r="B95" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="C95" t="s">
+        <v>330</v>
+      </c>
+      <c r="D95" t="s">
+        <v>331</v>
+      </c>
+      <c r="E95" t="s">
+        <v>719</v>
+      </c>
+      <c r="F95" t="s">
+        <v>720</v>
+      </c>
+      <c r="G95" t="s">
+        <v>721</v>
       </c>
       <c r="J95" s="2">
         <v>46122</v>
@@ -4326,9 +9881,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>95</v>
+      </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>99</v>
+      </c>
+      <c r="C96" t="s">
+        <v>332</v>
+      </c>
+      <c r="D96" t="s">
+        <v>333</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>727</v>
       </c>
       <c r="J96" s="2">
         <v>46125</v>
@@ -4337,9 +9910,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>96</v>
+      </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+      <c r="C97" t="s">
+        <v>334</v>
+      </c>
+      <c r="D97" t="s">
+        <v>335</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>726</v>
       </c>
       <c r="J97" s="2">
         <v>46126</v>
@@ -4348,9 +9939,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>97</v>
+      </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="C98" t="s">
+        <v>336</v>
+      </c>
+      <c r="D98" t="s">
+        <v>337</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>730</v>
       </c>
       <c r="J98" s="2">
         <v>46127</v>
@@ -4359,9 +9968,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>98</v>
+      </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="C99" t="s">
+        <v>338</v>
+      </c>
+      <c r="D99" t="s">
+        <v>339</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>733</v>
       </c>
       <c r="J99" s="2">
         <v>46128</v>
@@ -4370,9 +9997,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>99</v>
+      </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="C100" t="s">
+        <v>340</v>
+      </c>
+      <c r="D100" t="s">
+        <v>341</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>736</v>
       </c>
       <c r="J100" s="2">
         <v>46129</v>
@@ -4381,9 +10026,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>100</v>
+      </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="C101" t="s">
+        <v>342</v>
+      </c>
+      <c r="D101" t="s">
+        <v>343</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>739</v>
       </c>
       <c r="J101" s="2">
         <v>46132</v>
@@ -4392,9 +10055,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>101</v>
+      </c>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>105</v>
+      </c>
+      <c r="C102" t="s">
+        <v>344</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>742</v>
       </c>
       <c r="J102" s="2">
         <v>46133</v>
@@ -4403,9 +10084,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>102</v>
+      </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>346</v>
+      </c>
+      <c r="C103" t="s">
+        <v>347</v>
+      </c>
+      <c r="D103" t="s">
+        <v>348</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>745</v>
       </c>
       <c r="J103" s="2">
         <v>46134</v>
@@ -4414,9 +10113,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>103</v>
+      </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>106</v>
+      </c>
+      <c r="C104" t="s">
+        <v>349</v>
+      </c>
+      <c r="D104" t="s">
+        <v>350</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>748</v>
       </c>
       <c r="J104" s="2">
         <v>46136</v>
@@ -4425,10 +10142,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>104</v>
+      </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
+      <c r="C105" t="s">
+        <v>351</v>
+      </c>
+      <c r="D105" t="s">
+        <v>352</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>751</v>
+      </c>
       <c r="J105" s="2">
         <v>46139</v>
       </c>
@@ -4436,9 +10171,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>105</v>
+      </c>
       <c r="B106" t="s">
-        <v>275</v>
+        <v>257</v>
+      </c>
+      <c r="C106" t="s">
+        <v>353</v>
+      </c>
+      <c r="D106" t="s">
+        <v>354</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>754</v>
       </c>
       <c r="J106" s="2">
         <v>46140</v>
@@ -4447,9 +10200,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>106</v>
+      </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>107</v>
+      </c>
+      <c r="C107" t="s">
+        <v>355</v>
+      </c>
+      <c r="D107" t="s">
+        <v>356</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>757</v>
       </c>
       <c r="J107" s="2">
         <v>46141</v>
@@ -4458,9 +10229,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>107</v>
+      </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>108</v>
+      </c>
+      <c r="C108" t="s">
+        <v>357</v>
+      </c>
+      <c r="D108" t="s">
+        <v>358</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>760</v>
       </c>
       <c r="J108" s="2">
         <v>46142</v>
@@ -4469,9 +10258,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>108</v>
+      </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>109</v>
+      </c>
+      <c r="C109" t="s">
+        <v>359</v>
+      </c>
+      <c r="D109" t="s">
+        <v>360</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>763</v>
       </c>
       <c r="J109" s="2">
         <v>46146</v>
@@ -4480,9 +10287,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>109</v>
+      </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>110</v>
+      </c>
+      <c r="C110" t="s">
+        <v>361</v>
+      </c>
+      <c r="D110" t="s">
+        <v>362</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>766</v>
       </c>
       <c r="J110" s="2">
         <v>46147</v>
@@ -4491,9 +10316,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>110</v>
+      </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>111</v>
+      </c>
+      <c r="C111" t="s">
+        <v>363</v>
+      </c>
+      <c r="D111" t="s">
+        <v>364</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>769</v>
       </c>
       <c r="J111" s="2">
         <v>46148</v>
@@ -4502,9 +10345,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>111</v>
+      </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>112</v>
+      </c>
+      <c r="C112" t="s">
+        <v>365</v>
+      </c>
+      <c r="D112" t="s">
+        <v>366</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>772</v>
       </c>
       <c r="J112" s="2">
         <v>46149</v>
@@ -4513,9 +10374,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>112</v>
+      </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>367</v>
+      </c>
+      <c r="C113" t="s">
+        <v>368</v>
+      </c>
+      <c r="D113" t="s">
+        <v>369</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>775</v>
       </c>
       <c r="J113" s="2">
         <v>46150</v>
@@ -4524,9 +10403,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>113</v>
+      </c>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>370</v>
+      </c>
+      <c r="C114" t="s">
+        <v>371</v>
+      </c>
+      <c r="D114" t="s">
+        <v>372</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>778</v>
       </c>
       <c r="J114" s="2">
         <v>46153</v>
@@ -4535,9 +10432,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>114</v>
+      </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>113</v>
+      </c>
+      <c r="C115" t="s">
+        <v>373</v>
+      </c>
+      <c r="D115" t="s">
+        <v>374</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>781</v>
       </c>
       <c r="J115" s="2">
         <v>46154</v>
@@ -4546,9 +10461,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>115</v>
+      </c>
       <c r="B116" t="s">
-        <v>278</v>
+        <v>260</v>
+      </c>
+      <c r="C116" t="s">
+        <v>375</v>
+      </c>
+      <c r="D116" t="s">
+        <v>376</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>784</v>
       </c>
       <c r="J116" s="2">
         <v>46155</v>
@@ -4557,9 +10490,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>116</v>
+      </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>114</v>
+      </c>
+      <c r="C117" t="s">
+        <v>377</v>
+      </c>
+      <c r="D117" t="s">
+        <v>378</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>787</v>
       </c>
       <c r="J117" s="2">
         <v>46156</v>
@@ -4568,9 +10519,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>117</v>
+      </c>
       <c r="B118" t="s">
-        <v>126</v>
+        <v>379</v>
+      </c>
+      <c r="C118" t="s">
+        <v>380</v>
+      </c>
+      <c r="D118" t="s">
+        <v>381</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>790</v>
       </c>
       <c r="J118" s="2">
         <v>46157</v>
@@ -4579,9 +10548,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>118</v>
+      </c>
       <c r="B119" t="s">
-        <v>154</v>
+        <v>139</v>
+      </c>
+      <c r="C119" t="s">
+        <v>382</v>
+      </c>
+      <c r="D119" t="s">
+        <v>383</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="G119" t="s">
+        <v>793</v>
       </c>
       <c r="J119" s="2">
         <v>46160</v>
@@ -4590,9 +10577,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>119</v>
+      </c>
       <c r="B120" t="s">
-        <v>128</v>
+        <v>384</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>796</v>
       </c>
       <c r="J120" s="2">
         <v>46162</v>
@@ -4601,9 +10606,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>120</v>
+      </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>116</v>
+      </c>
+      <c r="C121" t="s">
+        <v>387</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="G121" t="s">
+        <v>799</v>
       </c>
       <c r="J121" s="2">
         <v>46163</v>
@@ -4612,9 +10635,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>121</v>
+      </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>117</v>
+      </c>
+      <c r="C122" t="s">
+        <v>389</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E122" t="s">
+        <v>800</v>
+      </c>
+      <c r="F122" t="s">
+        <v>801</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>802</v>
       </c>
       <c r="J122" s="2">
         <v>46164</v>
@@ -4623,9 +10664,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>122</v>
+      </c>
       <c r="B123" t="s">
-        <v>131</v>
+        <v>118</v>
+      </c>
+      <c r="C123" t="s">
+        <v>391</v>
+      </c>
+      <c r="D123" t="s">
+        <v>392</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="G123" t="s">
+        <v>805</v>
       </c>
       <c r="J123" s="2">
         <v>46167</v>
@@ -4634,9 +10693,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>123</v>
+      </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>119</v>
+      </c>
+      <c r="C124" t="s">
+        <v>393</v>
+      </c>
+      <c r="D124" t="s">
+        <v>394</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="F124" t="s">
+        <v>807</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>808</v>
       </c>
       <c r="J124" s="2">
         <v>46168</v>
@@ -4645,9 +10722,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>124</v>
+      </c>
       <c r="B125" t="s">
-        <v>133</v>
+        <v>120</v>
+      </c>
+      <c r="C125" t="s">
+        <v>396</v>
+      </c>
+      <c r="D125" t="s">
+        <v>397</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="G125" t="s">
+        <v>811</v>
       </c>
       <c r="J125" s="2">
         <v>46169</v>
@@ -4656,9 +10751,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>125</v>
+      </c>
       <c r="B126" t="s">
-        <v>134</v>
+        <v>121</v>
+      </c>
+      <c r="C126" t="s">
+        <v>398</v>
+      </c>
+      <c r="D126" t="s">
+        <v>399</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="F126" t="s">
+        <v>813</v>
+      </c>
+      <c r="G126" t="s">
+        <v>814</v>
       </c>
       <c r="J126" s="2">
         <v>46170</v>
@@ -4667,9 +10780,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>126</v>
+      </c>
       <c r="B127" t="s">
-        <v>135</v>
+        <v>122</v>
+      </c>
+      <c r="C127" t="s">
+        <v>400</v>
+      </c>
+      <c r="D127" t="s">
+        <v>401</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="F127" t="s">
+        <v>816</v>
+      </c>
+      <c r="G127" t="s">
+        <v>817</v>
       </c>
       <c r="J127" s="2">
         <v>46171</v>
@@ -4678,9 +10809,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>127</v>
+      </c>
       <c r="B128" t="s">
-        <v>136</v>
+        <v>123</v>
+      </c>
+      <c r="C128" t="s">
+        <v>402</v>
+      </c>
+      <c r="D128" t="s">
+        <v>403</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="F128" t="s">
+        <v>819</v>
+      </c>
+      <c r="G128" t="s">
+        <v>820</v>
       </c>
       <c r="J128" s="2">
         <v>46174</v>
@@ -4689,9 +10838,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>128</v>
+      </c>
       <c r="B129" t="s">
-        <v>137</v>
+        <v>124</v>
+      </c>
+      <c r="C129" t="s">
+        <v>404</v>
+      </c>
+      <c r="D129" t="s">
+        <v>405</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="F129" t="s">
+        <v>822</v>
+      </c>
+      <c r="G129" t="s">
+        <v>823</v>
       </c>
       <c r="J129" s="2">
         <v>46175</v>
@@ -4700,9 +10867,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>129</v>
+      </c>
       <c r="B130" t="s">
-        <v>138</v>
+        <v>125</v>
+      </c>
+      <c r="C130" t="s">
+        <v>406</v>
+      </c>
+      <c r="D130" t="s">
+        <v>407</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="F130" t="s">
+        <v>825</v>
+      </c>
+      <c r="G130" t="s">
+        <v>826</v>
       </c>
       <c r="J130" s="2">
         <v>46176</v>
@@ -4711,9 +10896,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>130</v>
+      </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>126</v>
+      </c>
+      <c r="C131" t="s">
+        <v>408</v>
+      </c>
+      <c r="D131" t="s">
+        <v>409</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="F131" t="s">
+        <v>828</v>
+      </c>
+      <c r="G131" t="s">
+        <v>829</v>
       </c>
       <c r="J131" s="2">
         <v>46177</v>
@@ -4722,9 +10925,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>131</v>
+      </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>127</v>
+      </c>
+      <c r="C132" t="s">
+        <v>410</v>
+      </c>
+      <c r="D132" t="s">
+        <v>411</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="F132" t="s">
+        <v>831</v>
+      </c>
+      <c r="G132" t="s">
+        <v>832</v>
       </c>
       <c r="J132" s="2">
         <v>46178</v>
@@ -4733,9 +10954,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>132</v>
+      </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>412</v>
+      </c>
+      <c r="C133" t="s">
+        <v>413</v>
+      </c>
+      <c r="D133" t="s">
+        <v>414</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="F133" t="s">
+        <v>834</v>
+      </c>
+      <c r="G133" t="s">
+        <v>835</v>
       </c>
       <c r="J133" s="2">
         <v>46181</v>
@@ -4744,9 +10983,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>133</v>
+      </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>128</v>
+      </c>
+      <c r="C134" t="s">
+        <v>415</v>
+      </c>
+      <c r="D134" t="s">
+        <v>416</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="F134" t="s">
+        <v>837</v>
+      </c>
+      <c r="G134" t="s">
+        <v>838</v>
       </c>
       <c r="J134" s="2">
         <v>46182</v>
@@ -4755,9 +11012,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>134</v>
+      </c>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>129</v>
+      </c>
+      <c r="C135" t="s">
+        <v>417</v>
+      </c>
+      <c r="D135" t="s">
+        <v>418</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="F135" t="s">
+        <v>840</v>
+      </c>
+      <c r="G135" t="s">
+        <v>841</v>
       </c>
       <c r="J135" s="2">
         <v>46183</v>
@@ -4766,9 +11041,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>135</v>
+      </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>130</v>
+      </c>
+      <c r="C136" t="s">
+        <v>419</v>
+      </c>
+      <c r="D136" t="s">
+        <v>420</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="F136" t="s">
+        <v>843</v>
+      </c>
+      <c r="G136" t="s">
+        <v>844</v>
       </c>
       <c r="J136" s="2">
         <v>46184</v>
@@ -4777,9 +11070,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>136</v>
+      </c>
       <c r="B137" t="s">
-        <v>145</v>
+        <v>131</v>
+      </c>
+      <c r="C137" t="s">
+        <v>421</v>
+      </c>
+      <c r="D137" t="s">
+        <v>422</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="F137" t="s">
+        <v>846</v>
+      </c>
+      <c r="G137" t="s">
+        <v>847</v>
       </c>
       <c r="J137" s="2">
         <v>46185</v>
@@ -4788,9 +11099,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>137</v>
+      </c>
       <c r="B138" t="s">
-        <v>146</v>
+        <v>395</v>
+      </c>
+      <c r="C138" t="s">
+        <v>423</v>
+      </c>
+      <c r="D138" t="s">
+        <v>424</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="F138" t="s">
+        <v>849</v>
+      </c>
+      <c r="G138" t="s">
+        <v>850</v>
       </c>
       <c r="J138" s="2">
         <v>46188</v>
@@ -4799,9 +11128,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>138</v>
+      </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>132</v>
+      </c>
+      <c r="C139" t="s">
+        <v>425</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="F139" t="s">
+        <v>852</v>
+      </c>
+      <c r="G139" t="s">
+        <v>853</v>
       </c>
       <c r="J139" s="2">
         <v>46189</v>
@@ -4810,9 +11157,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>139</v>
+      </c>
       <c r="B140" t="s">
-        <v>148</v>
+        <v>133</v>
+      </c>
+      <c r="C140" t="s">
+        <v>427</v>
+      </c>
+      <c r="D140" t="s">
+        <v>428</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="F140" t="s">
+        <v>855</v>
+      </c>
+      <c r="G140" t="s">
+        <v>856</v>
       </c>
       <c r="J140" s="2">
         <v>46190</v>
@@ -4821,9 +11186,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>140</v>
+      </c>
       <c r="B141" t="s">
-        <v>149</v>
+        <v>134</v>
+      </c>
+      <c r="C141" t="s">
+        <v>429</v>
+      </c>
+      <c r="D141" t="s">
+        <v>430</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="F141" t="s">
+        <v>858</v>
+      </c>
+      <c r="G141" t="s">
+        <v>859</v>
       </c>
       <c r="J141" s="2">
         <v>46191</v>
@@ -4832,9 +11215,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>141</v>
+      </c>
       <c r="B142" t="s">
-        <v>150</v>
+        <v>135</v>
+      </c>
+      <c r="C142" t="s">
+        <v>431</v>
+      </c>
+      <c r="D142" t="s">
+        <v>432</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="F142" t="s">
+        <v>861</v>
+      </c>
+      <c r="G142" s="9" t="s">
+        <v>862</v>
       </c>
       <c r="J142" s="2">
         <v>46192</v>
@@ -4843,9 +11244,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>142</v>
+      </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>136</v>
+      </c>
+      <c r="C143" t="s">
+        <v>433</v>
+      </c>
+      <c r="D143" t="s">
+        <v>434</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="F143" t="s">
+        <v>864</v>
+      </c>
+      <c r="G143" t="s">
+        <v>865</v>
       </c>
       <c r="J143" s="2">
         <v>46195</v>
@@ -4854,9 +11273,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>143</v>
+      </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>137</v>
+      </c>
+      <c r="C144" t="s">
+        <v>435</v>
+      </c>
+      <c r="D144" t="s">
+        <v>436</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="F144" t="s">
+        <v>867</v>
+      </c>
+      <c r="G144" t="s">
+        <v>868</v>
       </c>
       <c r="J144" s="2">
         <v>46196</v>
@@ -4865,9 +11302,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>144</v>
+      </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>138</v>
+      </c>
+      <c r="C145" t="s">
+        <v>437</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="F145" t="s">
+        <v>870</v>
+      </c>
+      <c r="G145" t="s">
+        <v>871</v>
       </c>
       <c r="J145" s="2">
         <v>46197</v>
@@ -4876,9 +11331,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>145</v>
+      </c>
       <c r="B146" t="s">
-        <v>127</v>
+        <v>115</v>
+      </c>
+      <c r="C146" t="s">
+        <v>439</v>
+      </c>
+      <c r="D146" t="s">
+        <v>440</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="F146" t="s">
+        <v>873</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>874</v>
       </c>
       <c r="J146" s="2">
         <v>46198</v>
@@ -4887,9 +11360,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>146</v>
+      </c>
       <c r="B147" t="s">
-        <v>155</v>
+        <v>140</v>
+      </c>
+      <c r="C147" t="s">
+        <v>441</v>
+      </c>
+      <c r="D147" t="s">
+        <v>442</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="F147" t="s">
+        <v>876</v>
+      </c>
+      <c r="G147" t="s">
+        <v>877</v>
       </c>
       <c r="J147" s="2">
         <v>46199</v>
@@ -4901,6 +11392,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
+++ b/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr backupFile="1" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CENGİZ\Desktop\EVOKUL\DILIMIZINZENGINLIKLERI2\bin\Debug\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F76249-AE23-4433-89C7-126C3F2AF9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KELIMELER" sheetId="1" r:id="rId1"/>
@@ -6539,9 +6545,6 @@
     <t>“Üzüm üzüme baka baka kararır.”</t>
   </si>
   <si>
-    <t>"Hatasız kul olmaz"</t>
-  </si>
-  <si>
     <t>Orhan Gencebay</t>
   </si>
   <si>
@@ -6554,13 +6557,16 @@
     <t>“Hak yolunda yürüyen yorulmaz.”</t>
   </si>
   <si>
-    <t>Söz gümüşse, sükût altındır</t>
+    <t>Söz gümüşse, sükût altındır.</t>
+  </si>
+  <si>
+    <t>"Hatasız kul olmaz."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -6664,9 +6670,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Ofis Teması">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Ofis">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6704,7 +6710,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Ofis">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -6776,7 +6782,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Ofis">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6949,22 +6955,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K147"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.42578125" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.44140625" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="75.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="94.42578125" customWidth="1"/>
+    <col min="7" max="7" width="75.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="94.44140625" customWidth="1"/>
     <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="12.109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6999,7 +7005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7028,13 +7034,13 @@
         <v>909</v>
       </c>
       <c r="J2" s="2">
-        <v>45967</v>
+        <v>45978</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7069,7 +7075,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7104,7 +7110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7139,7 +7145,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7174,7 +7180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7209,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7244,7 +7250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7279,7 +7285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7314,7 +7320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7343,7 +7349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7378,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7413,7 +7419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7448,7 +7454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -7483,7 +7489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7518,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -7553,7 +7559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -7588,7 +7594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -7623,7 +7629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -7658,7 +7664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -7693,7 +7699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7728,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7763,7 +7769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7798,7 +7804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7833,7 +7839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7868,7 +7874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7891,19 +7897,19 @@
         <v>521</v>
       </c>
       <c r="H27" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>919</v>
-      </c>
       <c r="J27" s="2">
-        <v>45968</v>
+        <v>46013</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7926,7 +7932,7 @@
         <v>524</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>902</v>
@@ -7938,7 +7944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -7958,7 +7964,7 @@
         <v>527</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>902</v>
@@ -7970,7 +7976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -7990,7 +7996,7 @@
         <v>530</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J30" s="2">
         <v>46016</v>
@@ -7999,7 +8005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8022,7 +8028,7 @@
         <v>533</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J31" s="2">
         <v>46017</v>
@@ -8031,7 +8037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8060,7 +8066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8089,7 +8095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8118,7 +8124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8147,7 +8153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8176,7 +8182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8205,7 +8211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -8234,7 +8240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8263,7 +8269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8292,7 +8298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8321,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8350,7 +8356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8379,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8408,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8437,7 +8443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8466,7 +8472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8495,7 +8501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8524,7 +8530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8550,7 +8556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8579,7 +8585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8608,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8637,7 +8643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8666,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8695,7 +8701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8724,7 +8730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8753,7 +8759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8782,7 +8788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8811,7 +8817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8840,7 +8846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8869,7 +8875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -8898,7 +8904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -8927,7 +8933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -8956,7 +8962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -8985,7 +8991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9014,7 +9020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9043,7 +9049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9072,7 +9078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9101,7 +9107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9130,7 +9136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9159,7 +9165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9188,7 +9194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9217,7 +9223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9246,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9275,7 +9281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9304,7 +9310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9333,7 +9339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9362,7 +9368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9391,7 +9397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9420,7 +9426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9449,7 +9455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9478,7 +9484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -9507,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9536,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9565,7 +9571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9594,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9623,7 +9629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9649,7 +9655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9678,7 +9684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -9707,7 +9713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -9736,7 +9742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9765,7 +9771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9794,7 +9800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9823,7 +9829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9852,7 +9858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9881,7 +9887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9910,7 +9916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9939,7 +9945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9968,7 +9974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9997,7 +10003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -10026,7 +10032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -10055,7 +10061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -10084,7 +10090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -10113,7 +10119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10142,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10171,7 +10177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10200,7 +10206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10229,7 +10235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10258,7 +10264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10287,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10316,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10345,7 +10351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10374,7 +10380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10403,7 +10409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10432,7 +10438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10461,7 +10467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10490,7 +10496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10519,7 +10525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10548,7 +10554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10577,7 +10583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10606,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10635,7 +10641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10664,7 +10670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10693,7 +10699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10722,7 +10728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10751,7 +10757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -10780,7 +10786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10809,7 +10815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -10838,7 +10844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10867,7 +10873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10896,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10925,7 +10931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10954,7 +10960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10983,7 +10989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -11012,7 +11018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -11041,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -11070,7 +11076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -11099,7 +11105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -11128,7 +11134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -11157,7 +11163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -11186,7 +11192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -11215,7 +11221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -11244,7 +11250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -11273,7 +11279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -11302,7 +11308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -11331,7 +11337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -11360,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>

--- a/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
+++ b/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CENGİZ\Desktop\EVOKUL\DILIMIZINZENGINLIKLERI2\bin\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F76249-AE23-4433-89C7-126C3F2AF9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07041174-0D36-4726-8B9E-3904FAE1391E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="1056">
   <si>
     <t>Id</t>
   </si>
@@ -6476,9 +6476,6 @@
     <t>“Güçlü olan, kendine hâkim olandır.”</t>
   </si>
   <si>
-    <t>Hz. Ali (r.a.)</t>
-  </si>
-  <si>
     <t>Hz. Ali</t>
   </si>
   <si>
@@ -6557,17 +6554,416 @@
     <t>“Hak yolunda yürüyen yorulmaz.”</t>
   </si>
   <si>
-    <t>Söz gümüşse, sükût altındır.</t>
+    <t>"Söz gümüşse, sükût altındır."</t>
+  </si>
+  <si>
+    <t>"Derdi dünya olanın, dünya kadar derdi olur."</t>
+  </si>
+  <si>
+    <t>"Komşu komşunun külüne muhtaçtır."</t>
+  </si>
+  <si>
+    <t>"Ne ekersen, onu biçersin."</t>
+  </si>
+  <si>
+    <t>"Lafla peynir gemisi yürümez."</t>
+  </si>
+  <si>
+    <t>"Gülme komşuna, gelir başına."</t>
+  </si>
+  <si>
+    <t>"Yalancının mumu yatsıya kadar yanar."</t>
+  </si>
+  <si>
+    <t>"Hayatta en hakiki mürşit ilimdir."</t>
+  </si>
+  <si>
+    <t>Atatürk</t>
+  </si>
+  <si>
+    <t>"Sevelim , sevilelim;dünya kimseye kalmaz.</t>
+  </si>
+  <si>
+    <t>"Yaşadığım her şey, hatırladıklarımdan ibaret."</t>
+  </si>
+  <si>
+    <t>Ahmet Hamdi Tanpınar</t>
+  </si>
+  <si>
+    <t>Özdemir Asaf</t>
+  </si>
+  <si>
+    <t>"Sessizlik bazen en güçlü cevaptır."</t>
+  </si>
+  <si>
+    <t>"Kim var diye seslenilince, sağına soluna bakmadan ben varım diyebilmektir adamlık."</t>
+  </si>
+  <si>
+    <t>Necip Fazıl KISAKÜREK</t>
+  </si>
+  <si>
+    <t>"Dostun attığı gül bile yaralar."</t>
+  </si>
+  <si>
+    <t>"Güneş balçıkla sıvanmaz."</t>
+  </si>
+  <si>
+    <t>"Her koyun kendi bacağından asılır."</t>
+  </si>
+  <si>
+    <t>"Misafir umduğunu değil bulduğunu yer."</t>
+  </si>
+  <si>
+    <t>"Güzellik geçicidir, iyilik kalıcı."</t>
+  </si>
+  <si>
+    <t>Anonim</t>
+  </si>
+  <si>
+    <t>"Ucuz etin yahnisi yenmez."</t>
+  </si>
+  <si>
+    <t>"Dert insana yol öğretir."</t>
+  </si>
+  <si>
+    <t>"Anlatmam derdimi dertsiz insana, dert çekmeyen dert kıymetin bilemez."</t>
+  </si>
+  <si>
+    <t>Aşık Veysel</t>
+  </si>
+  <si>
+    <t>"Vakit nakittir."</t>
+  </si>
+  <si>
+    <t>"Yüksek dağın dumanı çok olur."</t>
+  </si>
+  <si>
+    <t>"Yalancının evi yanmış, kimse inanmamış."</t>
   </si>
   <si>
     <t>"Hatasız kul olmaz."</t>
+  </si>
+  <si>
+    <t>"Sabırla koruk, helva olur."</t>
+  </si>
+  <si>
+    <t>"Düşmez, kalkmaz bir Allah'tır."</t>
+  </si>
+  <si>
+    <t>"Gülü seven dikenine katlanır."</t>
+  </si>
+  <si>
+    <t>"Bir gün bakarsın herkes gider."</t>
+  </si>
+  <si>
+    <t>Edip Cansever</t>
+  </si>
+  <si>
+    <t>"Tohum saç, bitmezse toprak utansın."</t>
+  </si>
+  <si>
+    <t>"Bir çocuğun düşleri, bir ülkenin geleceğidir."</t>
+  </si>
+  <si>
+    <t>Sunay Akın</t>
+  </si>
+  <si>
+    <t>"Karanlık, ışığın yokluğu değil bilginin ışığıdır."</t>
+  </si>
+  <si>
+    <t>Alev Alatlı</t>
+  </si>
+  <si>
+    <t>"Zaman en iyi öğretmendir."</t>
+  </si>
+  <si>
+    <t>"At, sahibine göre kişner."</t>
+  </si>
+  <si>
+    <t>"El elin eşeğini türkü söyleyerek arar."</t>
+  </si>
+  <si>
+    <t>"Tok açın halinden anlamaz."</t>
+  </si>
+  <si>
+    <t>"Gecenin hayrından sabahın şerri iyidir."</t>
+  </si>
+  <si>
+    <t>"Adalet mülkün temelidir."</t>
+  </si>
+  <si>
+    <t>Hz. Ömer</t>
+  </si>
+  <si>
+    <t>"Sakınılan göze çöp batar."</t>
+  </si>
+  <si>
+    <t>"Acele işe şeytan karışır."</t>
+  </si>
+  <si>
+    <t>"Abanın kadri yağmurda bilinir."</t>
+  </si>
+  <si>
+    <t>"Adam olana bir söz yeter."</t>
+  </si>
+  <si>
+    <t>"Parça bütünün habercisidir."</t>
+  </si>
+  <si>
+    <t>“Güzel gören güzel düşünür, güzel düşünen hayatından lezzet alır.”</t>
+  </si>
+  <si>
+    <t>"Bıçak yarası geçer, dil yarası geçmez."</t>
+  </si>
+  <si>
+    <t>"Cahil dosttan, akıllı düşman yeğdir."</t>
+  </si>
+  <si>
+    <t>Nabi</t>
+  </si>
+  <si>
+    <t>"Bâğ-ı dehrin hem hazânın hem bahârın görmüşüz. Biz neşâtın da gamın da rûzigârın görmüşüz."</t>
+  </si>
+  <si>
+    <t>“Beni hor görme kardeşim, sen altınsın ben tunç muyum?”</t>
+  </si>
+  <si>
+    <t>"Dağ ne kadar yüce olsa, yol üstünden aşar."</t>
+  </si>
+  <si>
+    <t>"El eli yıkar, el de yüzü."</t>
+  </si>
+  <si>
+    <t>"Bir mıh bir nal kurtarır, bir nal bir at kurtarır."</t>
+  </si>
+  <si>
+    <t>"Gözden ırak olan gönülden de ırak olur."</t>
+  </si>
+  <si>
+    <t>"İyiliğe iyilik her kişinin kârı, kötülüğe iyilik er kişinin kârı."</t>
+  </si>
+  <si>
+    <t>"Mart kapıdan baktırır, kazma kürek yaktırır."</t>
+  </si>
+  <si>
+    <t>"Minareyi çalan kılıfını hazırlar."</t>
+  </si>
+  <si>
+    <t>"Davulun sesi uzaktan hoş gelir."</t>
+  </si>
+  <si>
+    <t>"Dost başa, düşman ayağa bakar."</t>
+  </si>
+  <si>
+    <t>"Her yiğidin bir yoğurt yeyişi vardır."</t>
+  </si>
+  <si>
+    <t>"Körle yatan şaşı kalkar."</t>
+  </si>
+  <si>
+    <t>"Akıllı köprü arayıncaya dek deli suyu geçer."</t>
+  </si>
+  <si>
+    <t>"Bedava sirke baldan tatlıdır."</t>
+  </si>
+  <si>
+    <t>"Beterin beteri var."</t>
+  </si>
+  <si>
+    <t>"Cahile söz (laf) anlatmak, deveye hendek atlatmaktan güçtür (zordur)."</t>
+  </si>
+  <si>
+    <t>"Cahilin dostluğundan, âlimin düşmanlığı yeğdir."</t>
+  </si>
+  <si>
+    <t>"Can canın yoldaşıdır."</t>
+  </si>
+  <si>
+    <t>"(Çok) Havlayan köpek ısırmaz."</t>
+  </si>
+  <si>
+    <t>"Çok konuşan çok yanılır."</t>
+  </si>
+  <si>
+    <t>"Çok mal haramsız, çok laf yalansız olmaz."</t>
+  </si>
+  <si>
+    <t>"Dağ adamı, hasta eder sağ adamı."</t>
+  </si>
+  <si>
+    <t>"Dağ dağa kavuşmaz, insan insana kavuşur."</t>
+  </si>
+  <si>
+    <t>"Erkek arslan arslan da dişi arslan arslan değil mi?"</t>
+  </si>
+  <si>
+    <t>"Er olan ekmeğini taştan çıkarır."</t>
+  </si>
+  <si>
+    <t>"Eski dost düşman olmaz, yenisinden vefa gelmez."</t>
+  </si>
+  <si>
+    <t>" Eşeğe altın semer vursalar yine eşektir."</t>
+  </si>
+  <si>
+    <t>"Eşeğin kuyruğunu kalabalıkta kesme; kimi uzun der, kimi kısa."</t>
+  </si>
+  <si>
+    <t>"Gelene git denilmez."</t>
+  </si>
+  <si>
+    <t>" Gelini ata bindirmişler, "ya nasip" demiş."</t>
+  </si>
+  <si>
+    <t>"Gönül kimi severse güzel odur."</t>
+  </si>
+  <si>
+    <t>"Gönülsüz yenen (istenmeyen) aş, ya karın ağrıtır ya baş."</t>
+  </si>
+  <si>
+    <t>"Görgülü kuşlar gördüğünü işler, görmedik kuşlar ne görsün ki ne işler?"</t>
+  </si>
+  <si>
+    <t>"Göz görmeyince gönül katlanır."</t>
+  </si>
+  <si>
+    <t>" Hangi gün vardır akşam olmadık."</t>
+  </si>
+  <si>
+    <t>"Harman döven öküzün ağzı bağlanmaz."</t>
+  </si>
+  <si>
+    <t>"Hayır işi uzat şerre dönsün, şer izi uzat hayra dönsün."</t>
+  </si>
+  <si>
+    <t>"İki dinle (bin işit) bir söyle. (Bir söyle, iki dinle)."</t>
+  </si>
+  <si>
+    <t>"İnsan eşek olunca semer vuran çok olur."</t>
+  </si>
+  <si>
+    <t>"İsteyenin bir yüzü kara, vermeyenin iki yüzü."</t>
+  </si>
+  <si>
+    <t>"İşten artmaz, dişten artar."</t>
+  </si>
+  <si>
+    <t>"İtin (köpeğin) duası kabul (makbul) olsa (-ydı) gökten kemik yağar (-di)."</t>
+  </si>
+  <si>
+    <t>"Kaçanın anası ağlamamış."</t>
+  </si>
+  <si>
+    <t>"Kan kus, "kızılcık şerbeti içtim" de."</t>
+  </si>
+  <si>
+    <t>"Kara gün karanp kalmaz (durmaz). (Koç yiğit bunalıp ölmez.)"</t>
+  </si>
+  <si>
+    <t>"Katrandan olmaz şeker, olsa da cinsine çeker."</t>
+  </si>
+  <si>
+    <t>"Kaz gelen yerden tavuk esirgenmez."</t>
+  </si>
+  <si>
+    <t>"Kedi uzanamadığı (yetişemediği) ciğere, pis (murdar) der."</t>
+  </si>
+  <si>
+    <t>"Kısmet ise gelir Hint'ten, Yemen'den, kısmet değilse ne gelir elden?"</t>
+  </si>
+  <si>
+    <t>"Kuru laf (boş lakırdı) karın doyurmaz."</t>
+  </si>
+  <si>
+    <t>"Mahkeme kadıya mülk değil."</t>
+  </si>
+  <si>
+    <t>"Mal canın yongasıdır."</t>
+  </si>
+  <si>
+    <t>"Minareyi yaptırmayan yerden bitmiş sanır (bitti beller)."</t>
+  </si>
+  <si>
+    <t>"Mühür kimde ise Süleyman odur."</t>
+  </si>
+  <si>
+    <t>"Ne oldum dememeli, ne olacağım demeli."</t>
+  </si>
+  <si>
+    <t>"Olmaz olmaz deme, olmaz olmaz."</t>
+  </si>
+  <si>
+    <t>"Öfkeyle kalkan zararla oturur."</t>
+  </si>
+  <si>
+    <t>"Önce iğneyi kendine batır, sonra çuvaldızı ele."</t>
+  </si>
+  <si>
+    <t>"Para isteme benden, buz gibi soğurum senden."</t>
+  </si>
+  <si>
+    <t>"Pek yaş olma, sıkılırsın; pek de kuru olma, kırılırsın."</t>
+  </si>
+  <si>
+    <t>"Sakla beni varken, bulunayım sana yokken."</t>
+  </si>
+  <si>
+    <t>"Şakanın sonu kakadır."</t>
+  </si>
+  <si>
+    <t>"Taş yerinde ağırdır."</t>
+  </si>
+  <si>
+    <t>Bir kişinin çıkar sağlamak, beğenilmek veya menfaat elde etmek amacıyla başkalarını aşırı övmesi, sürekli iltifat etmesi.</t>
+  </si>
+  <si>
+    <t>Patronun gözüne girmek için sürekli ona övgüler yağdıran kişi, adeta dalkavukluk yapıyordu.</t>
+  </si>
+  <si>
+    <t>Fikirlerine o kadar taassup gösteriyordu ki, başka görüşleri hiç dinlemiyordu.</t>
+  </si>
+  <si>
+    <t>Konuşmasındaki müphem ifadeler, dinleyenleri düşündürdü.</t>
+  </si>
+  <si>
+    <t>Kasvetli bir kış günü, dışarı çıkmak istemedim.</t>
+  </si>
+  <si>
+    <t>"Sırrını açma dostuna (dostunun dostu vardır) o da söyler dostuna."</t>
+  </si>
+  <si>
+    <t>"Görünen dağın (köyün) uzağı olmaz."</t>
+  </si>
+  <si>
+    <t>"Herkes ektiğini biçer."</t>
+  </si>
+  <si>
+    <t>"Bugünün işini yarına bırakma."</t>
+  </si>
+  <si>
+    <t>"Sen ağa, ben ağa; bu ineği kim sağa?"</t>
+  </si>
+  <si>
+    <t>"Sen değişirsen dünya değişir."</t>
+  </si>
+  <si>
+    <t>"Yaratılanı severim, yaratandan ötürü."</t>
+  </si>
+  <si>
+    <t>"Akıllı, söylemeden düşünür; akılsız düşünmeden söyler."</t>
+  </si>
+  <si>
+    <t>"Çivi çiviyi söker."</t>
+  </si>
+  <si>
+    <t>O, hiçbir zaman çıkarı için kula kulluk edenlerden olmadı.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -6609,6 +7005,13 @@
       <family val="1"/>
       <charset val="162"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="162"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6636,7 +7039,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -6652,6 +7055,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6956,16 +7360,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K152"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.44140625" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="75.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="94.44140625" customWidth="1"/>
-    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="87.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="96.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="82.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.109375" style="2" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" style="1"/>
   </cols>
@@ -7031,7 +7436,7 @@
         <v>882</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J2" s="2">
         <v>45978</v>
@@ -7276,7 +7681,7 @@
         <v>894</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J9" s="2">
         <v>45987</v>
@@ -7308,10 +7713,10 @@
         <v>469</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J10" s="2">
         <v>45988</v>
@@ -7327,6 +7732,12 @@
       <c r="B11" t="s">
         <v>473</v>
       </c>
+      <c r="C11" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1042</v>
+      </c>
       <c r="E11" t="s">
         <v>470</v>
       </c>
@@ -7337,10 +7748,10 @@
         <v>472</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>898</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>899</v>
       </c>
       <c r="J11" s="2">
         <v>45989</v>
@@ -7372,7 +7783,7 @@
         <v>476</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>895</v>
@@ -7407,10 +7818,10 @@
         <v>479</v>
       </c>
       <c r="H13" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>901</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>902</v>
       </c>
       <c r="J13" s="2">
         <v>45993</v>
@@ -7442,10 +7853,10 @@
         <v>482</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J14" s="2">
         <v>45994</v>
@@ -7477,7 +7888,7 @@
         <v>485</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>886</v>
@@ -7512,10 +7923,10 @@
         <v>488</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J16" s="2">
         <v>45996</v>
@@ -7547,10 +7958,10 @@
         <v>491</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J17" s="2">
         <v>45999</v>
@@ -7582,7 +7993,7 @@
         <v>494</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>886</v>
@@ -7617,10 +8028,10 @@
         <v>497</v>
       </c>
       <c r="H19" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>908</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>909</v>
       </c>
       <c r="J19" s="2">
         <v>46001</v>
@@ -7652,10 +8063,10 @@
         <v>500</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="J20" s="2">
         <v>46002</v>
@@ -7687,10 +8098,10 @@
         <v>503</v>
       </c>
       <c r="H21" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>912</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>913</v>
       </c>
       <c r="J21" s="2">
         <v>46003</v>
@@ -7757,10 +8168,10 @@
         <v>509</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J23" s="2">
         <v>46007</v>
@@ -7792,10 +8203,10 @@
         <v>512</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J24" s="2">
         <v>46008</v>
@@ -7827,10 +8238,10 @@
         <v>515</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J25" s="2">
         <v>46009</v>
@@ -7862,10 +8273,10 @@
         <v>518</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J26" s="2">
         <v>46010</v>
@@ -7897,13 +8308,13 @@
         <v>521</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>923</v>
+        <v>1049</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>918</v>
+        <v>901</v>
       </c>
       <c r="J27" s="2">
-        <v>46013</v>
+        <v>45968</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -7932,10 +8343,10 @@
         <v>524</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J28" s="2">
         <v>46014</v>
@@ -7954,6 +8365,9 @@
       <c r="C29" t="s">
         <v>195</v>
       </c>
+      <c r="D29" s="8" t="s">
+        <v>1043</v>
+      </c>
       <c r="E29" t="s">
         <v>525</v>
       </c>
@@ -7964,10 +8378,10 @@
         <v>527</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J29" s="2">
         <v>46015</v>
@@ -7986,6 +8400,9 @@
       <c r="C30" t="s">
         <v>194</v>
       </c>
+      <c r="D30" s="8" t="s">
+        <v>1044</v>
+      </c>
       <c r="E30" t="s">
         <v>528</v>
       </c>
@@ -7996,7 +8413,10 @@
         <v>530</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>921</v>
+        <v>920</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J30" s="2">
         <v>46016</v>
@@ -8028,7 +8448,10 @@
         <v>533</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>922</v>
+        <v>921</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J31" s="2">
         <v>46017</v>
@@ -8059,6 +8482,12 @@
       <c r="G32" t="s">
         <v>536</v>
       </c>
+      <c r="H32" t="s">
+        <v>922</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J32" s="2">
         <v>46020</v>
       </c>
@@ -8088,6 +8517,12 @@
       <c r="G33" t="s">
         <v>539</v>
       </c>
+      <c r="H33" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J33" s="2">
         <v>46021</v>
       </c>
@@ -8117,6 +8552,12 @@
       <c r="G34" t="s">
         <v>542</v>
       </c>
+      <c r="H34" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J34" s="2">
         <v>46022</v>
       </c>
@@ -8146,6 +8587,12 @@
       <c r="G35" t="s">
         <v>545</v>
       </c>
+      <c r="H35" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J35" s="2">
         <v>46024</v>
       </c>
@@ -8175,6 +8622,12 @@
       <c r="G36" t="s">
         <v>548</v>
       </c>
+      <c r="H36" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J36" s="2">
         <v>46027</v>
       </c>
@@ -8204,6 +8657,12 @@
       <c r="G37" t="s">
         <v>551</v>
       </c>
+      <c r="H37" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J37" s="2">
         <v>46028</v>
       </c>
@@ -8233,6 +8692,12 @@
       <c r="G38" t="s">
         <v>554</v>
       </c>
+      <c r="H38" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>929</v>
+      </c>
       <c r="J38" s="2">
         <v>46029</v>
       </c>
@@ -8262,6 +8727,12 @@
       <c r="G39" t="s">
         <v>557</v>
       </c>
+      <c r="H39" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>886</v>
+      </c>
       <c r="J39" s="2">
         <v>46030</v>
       </c>
@@ -8291,6 +8762,12 @@
       <c r="G40" t="s">
         <v>560</v>
       </c>
+      <c r="H40" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>932</v>
+      </c>
       <c r="J40" s="2">
         <v>46031</v>
       </c>
@@ -8320,6 +8797,12 @@
       <c r="G41" t="s">
         <v>563</v>
       </c>
+      <c r="H41" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>933</v>
+      </c>
       <c r="J41" s="2">
         <v>46034</v>
       </c>
@@ -8349,6 +8832,12 @@
       <c r="G42" t="s">
         <v>566</v>
       </c>
+      <c r="H42" t="s">
+        <v>935</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>936</v>
+      </c>
       <c r="J42" s="2">
         <v>46035</v>
       </c>
@@ -8378,6 +8867,12 @@
       <c r="G43" t="s">
         <v>569</v>
       </c>
+      <c r="H43" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J43" s="2">
         <v>46036</v>
       </c>
@@ -8407,6 +8902,12 @@
       <c r="G44" t="s">
         <v>572</v>
       </c>
+      <c r="H44" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J44" s="2">
         <v>46037</v>
       </c>
@@ -8436,6 +8937,12 @@
       <c r="G45" t="s">
         <v>575</v>
       </c>
+      <c r="H45" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J45" s="2">
         <v>46038</v>
       </c>
@@ -8465,6 +8972,12 @@
       <c r="G46" t="s">
         <v>578</v>
       </c>
+      <c r="H46" s="8" t="s">
+        <v>940</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J46" s="2">
         <v>46055</v>
       </c>
@@ -8494,6 +9007,12 @@
       <c r="G47" t="s">
         <v>581</v>
       </c>
+      <c r="H47" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>942</v>
+      </c>
       <c r="J47" s="2">
         <v>46056</v>
       </c>
@@ -8523,6 +9042,12 @@
       <c r="G48" t="s">
         <v>586</v>
       </c>
+      <c r="H48" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J48" s="2">
         <v>46057</v>
       </c>
@@ -8549,6 +9074,15 @@
       <c r="F49" t="s">
         <v>583</v>
       </c>
+      <c r="G49" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J49" s="2">
         <v>46058</v>
       </c>
@@ -8578,6 +9112,12 @@
       <c r="G50" t="s">
         <v>589</v>
       </c>
+      <c r="H50" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>946</v>
+      </c>
       <c r="J50" s="2">
         <v>46059</v>
       </c>
@@ -8607,6 +9147,12 @@
       <c r="G51" t="s">
         <v>592</v>
       </c>
+      <c r="H51" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J51" s="2">
         <v>46062</v>
       </c>
@@ -8636,6 +9182,12 @@
       <c r="G52" t="s">
         <v>879</v>
       </c>
+      <c r="H52" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J52" s="2">
         <v>46063</v>
       </c>
@@ -8665,6 +9217,12 @@
       <c r="G53" t="s">
         <v>599</v>
       </c>
+      <c r="H53" s="8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J53" s="2">
         <v>46064</v>
       </c>
@@ -8694,6 +9252,12 @@
       <c r="G54" t="s">
         <v>601</v>
       </c>
+      <c r="H54" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J54" s="2">
         <v>46065</v>
       </c>
@@ -8723,6 +9287,12 @@
       <c r="G55" t="s">
         <v>603</v>
       </c>
+      <c r="H55" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>917</v>
+      </c>
       <c r="J55" s="2">
         <v>46066</v>
       </c>
@@ -8752,6 +9322,12 @@
       <c r="G56" t="s">
         <v>605</v>
       </c>
+      <c r="H56" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J56" s="2">
         <v>46069</v>
       </c>
@@ -8781,6 +9357,12 @@
       <c r="G57" t="s">
         <v>607</v>
       </c>
+      <c r="H57" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J57" s="2">
         <v>46070</v>
       </c>
@@ -8810,6 +9392,12 @@
       <c r="G58" t="s">
         <v>610</v>
       </c>
+      <c r="H58" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J58" s="2">
         <v>46071</v>
       </c>
@@ -8839,6 +9427,12 @@
       <c r="G59" t="s">
         <v>613</v>
       </c>
+      <c r="H59" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>955</v>
+      </c>
       <c r="J59" s="2">
         <v>46072</v>
       </c>
@@ -8868,6 +9462,12 @@
       <c r="G60" t="s">
         <v>616</v>
       </c>
+      <c r="H60" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>936</v>
+      </c>
       <c r="J60" s="2">
         <v>46073</v>
       </c>
@@ -8897,6 +9497,12 @@
       <c r="G61" t="s">
         <v>619</v>
       </c>
+      <c r="H61" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>958</v>
+      </c>
       <c r="J61" s="2">
         <v>46076</v>
       </c>
@@ -8926,6 +9532,12 @@
       <c r="G62" t="s">
         <v>622</v>
       </c>
+      <c r="H62" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="J62" s="2">
         <v>46077</v>
       </c>
@@ -8955,6 +9567,12 @@
       <c r="G63" t="s">
         <v>625</v>
       </c>
+      <c r="H63" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J63" s="2">
         <v>46078</v>
       </c>
@@ -8984,6 +9602,12 @@
       <c r="G64" t="s">
         <v>628</v>
       </c>
+      <c r="H64" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J64" s="2">
         <v>46079</v>
       </c>
@@ -9013,6 +9637,12 @@
       <c r="G65" t="s">
         <v>631</v>
       </c>
+      <c r="H65" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J65" s="2">
         <v>46080</v>
       </c>
@@ -9042,6 +9672,12 @@
       <c r="G66" t="s">
         <v>634</v>
       </c>
+      <c r="H66" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J66" s="2">
         <v>46083</v>
       </c>
@@ -9071,6 +9707,12 @@
       <c r="G67" t="s">
         <v>637</v>
       </c>
+      <c r="H67" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J67" s="2">
         <v>46084</v>
       </c>
@@ -9100,6 +9742,12 @@
       <c r="G68" t="s">
         <v>640</v>
       </c>
+      <c r="H68" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>967</v>
+      </c>
       <c r="J68" s="2">
         <v>46085</v>
       </c>
@@ -9129,6 +9777,12 @@
       <c r="G69" t="s">
         <v>643</v>
       </c>
+      <c r="H69" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J69" s="2">
         <v>46086</v>
       </c>
@@ -9158,6 +9812,12 @@
       <c r="G70" t="s">
         <v>646</v>
       </c>
+      <c r="H70" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J70" s="2">
         <v>46087</v>
       </c>
@@ -9187,6 +9847,12 @@
       <c r="G71" t="s">
         <v>649</v>
       </c>
+      <c r="H71" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J71" s="2">
         <v>46090</v>
       </c>
@@ -9216,6 +9882,12 @@
       <c r="G72" t="s">
         <v>652</v>
       </c>
+      <c r="H72" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J72" s="2">
         <v>46091</v>
       </c>
@@ -9245,6 +9917,12 @@
       <c r="G73" t="s">
         <v>655</v>
       </c>
+      <c r="H73" s="8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>888</v>
+      </c>
       <c r="J73" s="2">
         <v>46092</v>
       </c>
@@ -9274,6 +9952,12 @@
       <c r="G74" t="s">
         <v>658</v>
       </c>
+      <c r="H74" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>895</v>
+      </c>
       <c r="J74" s="2">
         <v>46093</v>
       </c>
@@ -9303,6 +9987,12 @@
       <c r="G75" t="s">
         <v>661</v>
       </c>
+      <c r="H75" t="s">
+        <v>973</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>888</v>
+      </c>
       <c r="J75" s="2">
         <v>46094</v>
       </c>
@@ -9332,6 +10022,12 @@
       <c r="G76" t="s">
         <v>664</v>
       </c>
+      <c r="H76" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J76" s="2">
         <v>46097</v>
       </c>
@@ -9361,6 +10057,12 @@
       <c r="G77" t="s">
         <v>667</v>
       </c>
+      <c r="H77" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J77" s="2">
         <v>46098</v>
       </c>
@@ -9390,6 +10092,12 @@
       <c r="G78" t="s">
         <v>670</v>
       </c>
+      <c r="H78" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>886</v>
+      </c>
       <c r="J78" s="2">
         <v>46099</v>
       </c>
@@ -9419,6 +10127,12 @@
       <c r="G79" t="s">
         <v>673</v>
       </c>
+      <c r="H79" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>976</v>
+      </c>
       <c r="J79" s="2">
         <v>46100</v>
       </c>
@@ -9448,6 +10162,12 @@
       <c r="G80" t="s">
         <v>676</v>
       </c>
+      <c r="H80" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>946</v>
+      </c>
       <c r="J80" s="2">
         <v>46101</v>
       </c>
@@ -9477,6 +10197,12 @@
       <c r="G81" t="s">
         <v>679</v>
       </c>
+      <c r="H81" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J81" s="2">
         <v>46104</v>
       </c>
@@ -9506,6 +10232,12 @@
       <c r="G82" t="s">
         <v>682</v>
       </c>
+      <c r="H82" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J82" s="2">
         <v>46105</v>
       </c>
@@ -9535,6 +10267,12 @@
       <c r="G83" t="s">
         <v>685</v>
       </c>
+      <c r="H83" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J83" s="2">
         <v>46106</v>
       </c>
@@ -9564,6 +10302,12 @@
       <c r="G84" t="s">
         <v>688</v>
       </c>
+      <c r="H84" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J84" s="2">
         <v>46107</v>
       </c>
@@ -9593,6 +10337,12 @@
       <c r="G85" t="s">
         <v>691</v>
       </c>
+      <c r="H85" s="8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J85" s="2">
         <v>46108</v>
       </c>
@@ -9622,6 +10372,12 @@
       <c r="G86" t="s">
         <v>694</v>
       </c>
+      <c r="H86" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J86" s="2">
         <v>46111</v>
       </c>
@@ -9639,6 +10395,9 @@
       <c r="C87" t="s">
         <v>313</v>
       </c>
+      <c r="D87" s="8" t="s">
+        <v>1045</v>
+      </c>
       <c r="E87" t="s">
         <v>695</v>
       </c>
@@ -9647,6 +10406,12 @@
       </c>
       <c r="G87" t="s">
         <v>697</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J87" s="2">
         <v>46112</v>
@@ -9677,6 +10442,12 @@
       <c r="G88" t="s">
         <v>700</v>
       </c>
+      <c r="H88" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J88" s="2">
         <v>46113</v>
       </c>
@@ -9706,6 +10477,12 @@
       <c r="G89" t="s">
         <v>703</v>
       </c>
+      <c r="H89" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J89" s="2">
         <v>46114</v>
       </c>
@@ -9735,6 +10512,12 @@
       <c r="G90" t="s">
         <v>706</v>
       </c>
+      <c r="H90" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J90" s="2">
         <v>46115</v>
       </c>
@@ -9764,6 +10547,12 @@
       <c r="G91" t="s">
         <v>709</v>
       </c>
+      <c r="H91" s="8" t="s">
+        <v>988</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J91" s="2">
         <v>46118</v>
       </c>
@@ -9793,6 +10582,12 @@
       <c r="G92" t="s">
         <v>712</v>
       </c>
+      <c r="H92" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J92" s="2">
         <v>46119</v>
       </c>
@@ -9822,6 +10617,12 @@
       <c r="G93" t="s">
         <v>715</v>
       </c>
+      <c r="H93" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J93" s="2">
         <v>46120</v>
       </c>
@@ -9851,6 +10652,12 @@
       <c r="G94" t="s">
         <v>718</v>
       </c>
+      <c r="H94" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J94" s="2">
         <v>46121</v>
       </c>
@@ -9880,6 +10687,12 @@
       <c r="G95" t="s">
         <v>721</v>
       </c>
+      <c r="H95" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J95" s="2">
         <v>46122</v>
       </c>
@@ -9909,6 +10722,12 @@
       <c r="G96" s="8" t="s">
         <v>727</v>
       </c>
+      <c r="H96" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J96" s="2">
         <v>46125</v>
       </c>
@@ -9938,6 +10757,12 @@
       <c r="G97" s="8" t="s">
         <v>726</v>
       </c>
+      <c r="H97" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J97" s="2">
         <v>46126</v>
       </c>
@@ -9967,6 +10792,12 @@
       <c r="G98" s="8" t="s">
         <v>730</v>
       </c>
+      <c r="H98" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J98" s="2">
         <v>46127</v>
       </c>
@@ -9996,6 +10827,12 @@
       <c r="G99" s="8" t="s">
         <v>733</v>
       </c>
+      <c r="H99" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J99" s="2">
         <v>46128</v>
       </c>
@@ -10025,6 +10862,12 @@
       <c r="G100" s="8" t="s">
         <v>736</v>
       </c>
+      <c r="H100" s="8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J100" s="2">
         <v>46129</v>
       </c>
@@ -10054,6 +10897,12 @@
       <c r="G101" s="8" t="s">
         <v>739</v>
       </c>
+      <c r="H101" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J101" s="2">
         <v>46132</v>
       </c>
@@ -10083,6 +10932,12 @@
       <c r="G102" s="8" t="s">
         <v>742</v>
       </c>
+      <c r="H102" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J102" s="2">
         <v>46133</v>
       </c>
@@ -10112,6 +10967,12 @@
       <c r="G103" s="8" t="s">
         <v>745</v>
       </c>
+      <c r="H103" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J103" s="2">
         <v>46134</v>
       </c>
@@ -10141,6 +11002,12 @@
       <c r="G104" s="8" t="s">
         <v>748</v>
       </c>
+      <c r="H104" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J104" s="2">
         <v>46136</v>
       </c>
@@ -10170,6 +11037,12 @@
       <c r="G105" s="8" t="s">
         <v>751</v>
       </c>
+      <c r="H105" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J105" s="2">
         <v>46139</v>
       </c>
@@ -10199,6 +11072,12 @@
       <c r="G106" s="8" t="s">
         <v>754</v>
       </c>
+      <c r="H106" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J106" s="2">
         <v>46140</v>
       </c>
@@ -10228,6 +11107,12 @@
       <c r="G107" s="8" t="s">
         <v>757</v>
       </c>
+      <c r="H107" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J107" s="2">
         <v>46141</v>
       </c>
@@ -10257,6 +11142,12 @@
       <c r="G108" s="8" t="s">
         <v>760</v>
       </c>
+      <c r="H108" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J108" s="2">
         <v>46142</v>
       </c>
@@ -10286,6 +11177,12 @@
       <c r="G109" s="8" t="s">
         <v>763</v>
       </c>
+      <c r="H109" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J109" s="2">
         <v>46146</v>
       </c>
@@ -10315,6 +11212,12 @@
       <c r="G110" s="8" t="s">
         <v>766</v>
       </c>
+      <c r="H110" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J110" s="2">
         <v>46147</v>
       </c>
@@ -10344,6 +11247,12 @@
       <c r="G111" s="8" t="s">
         <v>769</v>
       </c>
+      <c r="H111" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J111" s="2">
         <v>46148</v>
       </c>
@@ -10373,6 +11282,12 @@
       <c r="G112" s="8" t="s">
         <v>772</v>
       </c>
+      <c r="H112" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J112" s="2">
         <v>46149</v>
       </c>
@@ -10402,6 +11317,12 @@
       <c r="G113" s="8" t="s">
         <v>775</v>
       </c>
+      <c r="H113" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J113" s="2">
         <v>46150</v>
       </c>
@@ -10431,6 +11352,12 @@
       <c r="G114" s="8" t="s">
         <v>778</v>
       </c>
+      <c r="H114" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J114" s="2">
         <v>46153</v>
       </c>
@@ -10460,6 +11387,12 @@
       <c r="G115" s="8" t="s">
         <v>781</v>
       </c>
+      <c r="H115" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J115" s="2">
         <v>46154</v>
       </c>
@@ -10489,6 +11422,12 @@
       <c r="G116" s="8" t="s">
         <v>784</v>
       </c>
+      <c r="H116" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J116" s="2">
         <v>46155</v>
       </c>
@@ -10518,6 +11457,12 @@
       <c r="G117" s="8" t="s">
         <v>787</v>
       </c>
+      <c r="H117" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J117" s="2">
         <v>46156</v>
       </c>
@@ -10547,6 +11492,12 @@
       <c r="G118" s="8" t="s">
         <v>790</v>
       </c>
+      <c r="H118" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J118" s="2">
         <v>46157</v>
       </c>
@@ -10576,6 +11527,12 @@
       <c r="G119" t="s">
         <v>793</v>
       </c>
+      <c r="H119" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J119" s="2">
         <v>46160</v>
       </c>
@@ -10605,6 +11562,12 @@
       <c r="G120" s="8" t="s">
         <v>796</v>
       </c>
+      <c r="H120" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J120" s="2">
         <v>46162</v>
       </c>
@@ -10634,6 +11597,12 @@
       <c r="G121" t="s">
         <v>799</v>
       </c>
+      <c r="H121" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J121" s="2">
         <v>46163</v>
       </c>
@@ -10663,6 +11632,12 @@
       <c r="G122" s="8" t="s">
         <v>802</v>
       </c>
+      <c r="H122" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J122" s="2">
         <v>46164</v>
       </c>
@@ -10692,6 +11667,12 @@
       <c r="G123" t="s">
         <v>805</v>
       </c>
+      <c r="H123" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J123" s="2">
         <v>46167</v>
       </c>
@@ -10721,6 +11702,12 @@
       <c r="G124" s="9" t="s">
         <v>808</v>
       </c>
+      <c r="H124" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J124" s="2">
         <v>46168</v>
       </c>
@@ -10750,6 +11737,12 @@
       <c r="G125" t="s">
         <v>811</v>
       </c>
+      <c r="H125" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J125" s="2">
         <v>46169</v>
       </c>
@@ -10779,6 +11772,12 @@
       <c r="G126" t="s">
         <v>814</v>
       </c>
+      <c r="H126" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J126" s="2">
         <v>46170</v>
       </c>
@@ -10808,6 +11807,12 @@
       <c r="G127" t="s">
         <v>817</v>
       </c>
+      <c r="H127" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J127" s="2">
         <v>46171</v>
       </c>
@@ -10837,6 +11842,12 @@
       <c r="G128" t="s">
         <v>820</v>
       </c>
+      <c r="H128" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J128" s="2">
         <v>46174</v>
       </c>
@@ -10866,6 +11877,12 @@
       <c r="G129" t="s">
         <v>823</v>
       </c>
+      <c r="H129" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J129" s="2">
         <v>46175</v>
       </c>
@@ -10895,6 +11912,12 @@
       <c r="G130" t="s">
         <v>826</v>
       </c>
+      <c r="H130" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J130" s="2">
         <v>46176</v>
       </c>
@@ -10924,6 +11947,12 @@
       <c r="G131" t="s">
         <v>829</v>
       </c>
+      <c r="H131" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J131" s="2">
         <v>46177</v>
       </c>
@@ -10953,6 +11982,12 @@
       <c r="G132" t="s">
         <v>832</v>
       </c>
+      <c r="H132" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J132" s="2">
         <v>46178</v>
       </c>
@@ -10982,6 +12017,12 @@
       <c r="G133" t="s">
         <v>835</v>
       </c>
+      <c r="H133" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J133" s="2">
         <v>46181</v>
       </c>
@@ -11011,6 +12052,12 @@
       <c r="G134" t="s">
         <v>838</v>
       </c>
+      <c r="H134" s="8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J134" s="2">
         <v>46182</v>
       </c>
@@ -11040,6 +12087,12 @@
       <c r="G135" t="s">
         <v>841</v>
       </c>
+      <c r="H135" s="8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J135" s="2">
         <v>46183</v>
       </c>
@@ -11069,6 +12122,12 @@
       <c r="G136" t="s">
         <v>844</v>
       </c>
+      <c r="H136" s="8" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J136" s="2">
         <v>46184</v>
       </c>
@@ -11098,6 +12157,12 @@
       <c r="G137" t="s">
         <v>847</v>
       </c>
+      <c r="H137" s="8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I137" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J137" s="2">
         <v>46185</v>
       </c>
@@ -11127,6 +12192,12 @@
       <c r="G138" t="s">
         <v>850</v>
       </c>
+      <c r="H138" s="8" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J138" s="2">
         <v>46188</v>
       </c>
@@ -11156,6 +12227,12 @@
       <c r="G139" t="s">
         <v>853</v>
       </c>
+      <c r="H139" s="8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J139" s="2">
         <v>46189</v>
       </c>
@@ -11185,6 +12262,12 @@
       <c r="G140" t="s">
         <v>856</v>
       </c>
+      <c r="H140" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J140" s="2">
         <v>46190</v>
       </c>
@@ -11214,6 +12297,12 @@
       <c r="G141" t="s">
         <v>859</v>
       </c>
+      <c r="H141" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I141" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J141" s="2">
         <v>46191</v>
       </c>
@@ -11243,6 +12332,12 @@
       <c r="G142" s="9" t="s">
         <v>862</v>
       </c>
+      <c r="H142" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I142" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J142" s="2">
         <v>46192</v>
       </c>
@@ -11272,6 +12367,12 @@
       <c r="G143" t="s">
         <v>865</v>
       </c>
+      <c r="H143" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J143" s="2">
         <v>46195</v>
       </c>
@@ -11301,6 +12402,12 @@
       <c r="G144" t="s">
         <v>868</v>
       </c>
+      <c r="H144" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I144" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J144" s="2">
         <v>46196</v>
       </c>
@@ -11330,6 +12437,12 @@
       <c r="G145" t="s">
         <v>871</v>
       </c>
+      <c r="H145" s="8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I145" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J145" s="2">
         <v>46197</v>
       </c>
@@ -11359,6 +12472,12 @@
       <c r="G146" s="9" t="s">
         <v>874</v>
       </c>
+      <c r="H146" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I146" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J146" s="2">
         <v>46198</v>
       </c>
@@ -11366,7 +12485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -11388,12 +12507,21 @@
       <c r="G147" t="s">
         <v>877</v>
       </c>
+      <c r="H147" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I147" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="J147" s="2">
         <v>46199</v>
       </c>
       <c r="K147" s="1">
         <v>0</v>
       </c>
+    </row>
+    <row r="152" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H152" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
+++ b/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="1055">
   <si>
     <t>Id</t>
   </si>
@@ -6470,9 +6470,6 @@
     <t>“Güçlü olan, kendine hâkim olandır.”</t>
   </si>
   <si>
-    <t>Hz. Ali (r.a.)</t>
-  </si>
-  <si>
     <t>Hz. Ali</t>
   </si>
   <si>
@@ -6539,9 +6536,6 @@
     <t>“Üzüm üzüme baka baka kararır.”</t>
   </si>
   <si>
-    <t>"Hatasız kul olmaz"</t>
-  </si>
-  <si>
     <t>Orhan Gencebay</t>
   </si>
   <si>
@@ -6554,14 +6548,413 @@
     <t>“Hak yolunda yürüyen yorulmaz.”</t>
   </si>
   <si>
-    <t>Söz gümüşse, sükût altındır</t>
+    <t>"Söz gümüşse, sükût altındır."</t>
+  </si>
+  <si>
+    <t>"Derdi dünya olanın, dünya kadar derdi olur."</t>
+  </si>
+  <si>
+    <t>"Komşu komşunun külüne muhtaçtır."</t>
+  </si>
+  <si>
+    <t>"Ne ekersen, onu biçersin."</t>
+  </si>
+  <si>
+    <t>"Lafla peynir gemisi yürümez."</t>
+  </si>
+  <si>
+    <t>"Gülme komşuna, gelir başına."</t>
+  </si>
+  <si>
+    <t>"Yalancının mumu yatsıya kadar yanar."</t>
+  </si>
+  <si>
+    <t>"Hayatta en hakiki mürşit ilimdir."</t>
+  </si>
+  <si>
+    <t>Atatürk</t>
+  </si>
+  <si>
+    <t>"Sevelim , sevilelim;dünya kimseye kalmaz.</t>
+  </si>
+  <si>
+    <t>"Yaşadığım her şey, hatırladıklarımdan ibaret."</t>
+  </si>
+  <si>
+    <t>Ahmet Hamdi Tanpınar</t>
+  </si>
+  <si>
+    <t>Özdemir Asaf</t>
+  </si>
+  <si>
+    <t>"Sessizlik bazen en güçlü cevaptır."</t>
+  </si>
+  <si>
+    <t>"Kim var diye seslenilince, sağına soluna bakmadan ben varım diyebilmektir adamlık."</t>
+  </si>
+  <si>
+    <t>Necip Fazıl KISAKÜREK</t>
+  </si>
+  <si>
+    <t>"Dostun attığı gül bile yaralar."</t>
+  </si>
+  <si>
+    <t>"Güneş balçıkla sıvanmaz."</t>
+  </si>
+  <si>
+    <t>"Her koyun kendi bacağından asılır."</t>
+  </si>
+  <si>
+    <t>"Misafir umduğunu değil bulduğunu yer."</t>
+  </si>
+  <si>
+    <t>"Güzellik geçicidir, iyilik kalıcı."</t>
+  </si>
+  <si>
+    <t>Anonim</t>
+  </si>
+  <si>
+    <t>"Ucuz etin yahnisi yenmez."</t>
+  </si>
+  <si>
+    <t>"Dert insana yol öğretir."</t>
+  </si>
+  <si>
+    <t>"Anlatmam derdimi dertsiz insana, dert çekmeyen dert kıymetin bilemez."</t>
+  </si>
+  <si>
+    <t>Aşık Veysel</t>
+  </si>
+  <si>
+    <t>"Vakit nakittir."</t>
+  </si>
+  <si>
+    <t>"Yüksek dağın dumanı çok olur."</t>
+  </si>
+  <si>
+    <t>"Yalancının evi yanmış, kimse inanmamış."</t>
+  </si>
+  <si>
+    <t>"Hatasız kul olmaz."</t>
+  </si>
+  <si>
+    <t>"Sabırla koruk, helva olur."</t>
+  </si>
+  <si>
+    <t>"Düşmez, kalkmaz bir Allah'tır."</t>
+  </si>
+  <si>
+    <t>"Gülü seven dikenine katlanır."</t>
+  </si>
+  <si>
+    <t>"Bir gün bakarsın herkes gider."</t>
+  </si>
+  <si>
+    <t>Edip Cansever</t>
+  </si>
+  <si>
+    <t>"Tohum saç, bitmezse toprak utansın."</t>
+  </si>
+  <si>
+    <t>"Bir çocuğun düşleri, bir ülkenin geleceğidir."</t>
+  </si>
+  <si>
+    <t>Sunay Akın</t>
+  </si>
+  <si>
+    <t>"Karanlık, ışığın yokluğu değil bilginin ışığıdır."</t>
+  </si>
+  <si>
+    <t>Alev Alatlı</t>
+  </si>
+  <si>
+    <t>"Zaman en iyi öğretmendir."</t>
+  </si>
+  <si>
+    <t>"At, sahibine göre kişner."</t>
+  </si>
+  <si>
+    <t>"El elin eşeğini türkü söyleyerek arar."</t>
+  </si>
+  <si>
+    <t>"Tok açın halinden anlamaz."</t>
+  </si>
+  <si>
+    <t>"Gecenin hayrından sabahın şerri iyidir."</t>
+  </si>
+  <si>
+    <t>"Adalet mülkün temelidir."</t>
+  </si>
+  <si>
+    <t>Hz. Ömer</t>
+  </si>
+  <si>
+    <t>"Sakınılan göze çöp batar."</t>
+  </si>
+  <si>
+    <t>"Acele işe şeytan karışır."</t>
+  </si>
+  <si>
+    <t>"Abanın kadri yağmurda bilinir."</t>
+  </si>
+  <si>
+    <t>"Adam olana bir söz yeter."</t>
+  </si>
+  <si>
+    <t>"Parça bütünün habercisidir."</t>
+  </si>
+  <si>
+    <t>“Güzel gören güzel düşünür, güzel düşünen hayatından lezzet alır.”</t>
+  </si>
+  <si>
+    <t>"Bıçak yarası geçer, dil yarası geçmez."</t>
+  </si>
+  <si>
+    <t>"Cahil dosttan, akıllı düşman yeğdir."</t>
+  </si>
+  <si>
+    <t>Nabi</t>
+  </si>
+  <si>
+    <t>"Bâğ-ı dehrin hem hazânın hem bahârın görmüşüz. Biz neşâtın da gamın da rûzigârın görmüşüz."</t>
+  </si>
+  <si>
+    <t>“Beni hor görme kardeşim, sen altınsın ben tunç muyum?”</t>
+  </si>
+  <si>
+    <t>"Dağ ne kadar yüce olsa, yol üstünden aşar."</t>
+  </si>
+  <si>
+    <t>"El eli yıkar, el de yüzü."</t>
+  </si>
+  <si>
+    <t>"Bir mıh bir nal kurtarır, bir nal bir at kurtarır."</t>
+  </si>
+  <si>
+    <t>"Gözden ırak olan gönülden de ırak olur."</t>
+  </si>
+  <si>
+    <t>"İyiliğe iyilik her kişinin kârı, kötülüğe iyilik er kişinin kârı."</t>
+  </si>
+  <si>
+    <t>"Mart kapıdan baktırır, kazma kürek yaktırır."</t>
+  </si>
+  <si>
+    <t>"Minareyi çalan kılıfını hazırlar."</t>
+  </si>
+  <si>
+    <t>"Davulun sesi uzaktan hoş gelir."</t>
+  </si>
+  <si>
+    <t>"Dost başa, düşman ayağa bakar."</t>
+  </si>
+  <si>
+    <t>"Her yiğidin bir yoğurt yeyişi vardır."</t>
+  </si>
+  <si>
+    <t>"Körle yatan şaşı kalkar."</t>
+  </si>
+  <si>
+    <t>"Akıllı köprü arayıncaya dek deli suyu geçer."</t>
+  </si>
+  <si>
+    <t>"Bedava sirke baldan tatlıdır."</t>
+  </si>
+  <si>
+    <t>"Beterin beteri var."</t>
+  </si>
+  <si>
+    <t>"Cahile söz (laf) anlatmak, deveye hendek atlatmaktan güçtür (zordur)."</t>
+  </si>
+  <si>
+    <t>"Cahilin dostluğundan, âlimin düşmanlığı yeğdir."</t>
+  </si>
+  <si>
+    <t>"Can canın yoldaşıdır."</t>
+  </si>
+  <si>
+    <t>"(Çok) Havlayan köpek ısırmaz."</t>
+  </si>
+  <si>
+    <t>"Çok konuşan çok yanılır."</t>
+  </si>
+  <si>
+    <t>"Çok mal haramsız, çok laf yalansız olmaz."</t>
+  </si>
+  <si>
+    <t>"Dağ adamı, hasta eder sağ adamı."</t>
+  </si>
+  <si>
+    <t>"Dağ dağa kavuşmaz, insan insana kavuşur."</t>
+  </si>
+  <si>
+    <t>"Erkek arslan arslan da dişi arslan arslan değil mi?"</t>
+  </si>
+  <si>
+    <t>"Er olan ekmeğini taştan çıkarır."</t>
+  </si>
+  <si>
+    <t>"Eski dost düşman olmaz, yenisinden vefa gelmez."</t>
+  </si>
+  <si>
+    <t>" Eşeğe altın semer vursalar yine eşektir."</t>
+  </si>
+  <si>
+    <t>"Eşeğin kuyruğunu kalabalıkta kesme; kimi uzun der, kimi kısa."</t>
+  </si>
+  <si>
+    <t>"Gelene git denilmez."</t>
+  </si>
+  <si>
+    <t>" Gelini ata bindirmişler, "ya nasip" demiş."</t>
+  </si>
+  <si>
+    <t>"Gönül kimi severse güzel odur."</t>
+  </si>
+  <si>
+    <t>"Gönülsüz yenen (istenmeyen) aş, ya karın ağrıtır ya baş."</t>
+  </si>
+  <si>
+    <t>"Görgülü kuşlar gördüğünü işler, görmedik kuşlar ne görsün ki ne işler?"</t>
+  </si>
+  <si>
+    <t>"Göz görmeyince gönül katlanır."</t>
+  </si>
+  <si>
+    <t>" Hangi gün vardır akşam olmadık."</t>
+  </si>
+  <si>
+    <t>"Harman döven öküzün ağzı bağlanmaz."</t>
+  </si>
+  <si>
+    <t>"Hayır işi uzat şerre dönsün, şer izi uzat hayra dönsün."</t>
+  </si>
+  <si>
+    <t>"İki dinle (bin işit) bir söyle. (Bir söyle, iki dinle)."</t>
+  </si>
+  <si>
+    <t>"İnsan eşek olunca semer vuran çok olur."</t>
+  </si>
+  <si>
+    <t>"İsteyenin bir yüzü kara, vermeyenin iki yüzü."</t>
+  </si>
+  <si>
+    <t>"İşten artmaz, dişten artar."</t>
+  </si>
+  <si>
+    <t>"İtin (köpeğin) duası kabul (makbul) olsa (-ydı) gökten kemik yağar (-di)."</t>
+  </si>
+  <si>
+    <t>"Kaçanın anası ağlamamış."</t>
+  </si>
+  <si>
+    <t>"Kan kus, "kızılcık şerbeti içtim" de."</t>
+  </si>
+  <si>
+    <t>"Kara gün karanp kalmaz (durmaz). (Koç yiğit bunalıp ölmez.)"</t>
+  </si>
+  <si>
+    <t>"Katrandan olmaz şeker, olsa da cinsine çeker."</t>
+  </si>
+  <si>
+    <t>"Kaz gelen yerden tavuk esirgenmez."</t>
+  </si>
+  <si>
+    <t>"Kedi uzanamadığı (yetişemediği) ciğere, pis (murdar) der."</t>
+  </si>
+  <si>
+    <t>"Kısmet ise gelir Hint'ten, Yemen'den, kısmet değilse ne gelir elden?"</t>
+  </si>
+  <si>
+    <t>"Kuru laf (boş lakırdı) karın doyurmaz."</t>
+  </si>
+  <si>
+    <t>"Mahkeme kadıya mülk değil."</t>
+  </si>
+  <si>
+    <t>"Mal canın yongasıdır."</t>
+  </si>
+  <si>
+    <t>"Minareyi yaptırmayan yerden bitmiş sanır (bitti beller)."</t>
+  </si>
+  <si>
+    <t>"Mühür kimde ise Süleyman odur."</t>
+  </si>
+  <si>
+    <t>"Ne oldum dememeli, ne olacağım demeli."</t>
+  </si>
+  <si>
+    <t>"Olmaz olmaz deme, olmaz olmaz."</t>
+  </si>
+  <si>
+    <t>"Öfkeyle kalkan zararla oturur."</t>
+  </si>
+  <si>
+    <t>"Önce iğneyi kendine batır, sonra çuvaldızı ele."</t>
+  </si>
+  <si>
+    <t>"Para isteme benden, buz gibi soğurum senden."</t>
+  </si>
+  <si>
+    <t>"Pek yaş olma, sıkılırsın; pek de kuru olma, kırılırsın."</t>
+  </si>
+  <si>
+    <t>"Sakla beni varken, bulunayım sana yokken."</t>
+  </si>
+  <si>
+    <t>"Şakanın sonu kakadır."</t>
+  </si>
+  <si>
+    <t>"Taş yerinde ağırdır."</t>
+  </si>
+  <si>
+    <t>Bir kişinin çıkar sağlamak, beğenilmek veya menfaat elde etmek amacıyla başkalarını aşırı övmesi, sürekli iltifat etmesi.</t>
+  </si>
+  <si>
+    <t>Patronun gözüne girmek için sürekli ona övgüler yağdıran kişi, adeta dalkavukluk yapıyordu.</t>
+  </si>
+  <si>
+    <t>Fikirlerine o kadar taassup gösteriyordu ki, başka görüşleri hiç dinlemiyordu.</t>
+  </si>
+  <si>
+    <t>Konuşmasındaki müphem ifadeler, dinleyenleri düşündürdü.</t>
+  </si>
+  <si>
+    <t>Kasvetli bir kış günü, dışarı çıkmak istemedim.</t>
+  </si>
+  <si>
+    <t>"Sırrını açma dostuna (dostunun dostu vardır) o da söyler dostuna."</t>
+  </si>
+  <si>
+    <t>"Görünen dağın (köyün) uzağı olmaz."</t>
+  </si>
+  <si>
+    <t>"Herkes ektiğini biçer."</t>
+  </si>
+  <si>
+    <t>"Bugünün işini yarına bırakma."</t>
+  </si>
+  <si>
+    <t>"Sen ağa, ben ağa; bu ineği kim sağa?"</t>
+  </si>
+  <si>
+    <t>"Sen değişirsen dünya değişir."</t>
+  </si>
+  <si>
+    <t>"Yaratılanı severim, yaratandan ötürü."</t>
+  </si>
+  <si>
+    <t>"Akıllı, söylemeden düşünür; akılsız düşünmeden söyler."</t>
+  </si>
+  <si>
+    <t>"Çivi çiviyi söker."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -6603,6 +6996,13 @@
       <family val="1"/>
       <charset val="162"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="162"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6630,7 +7030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -6646,6 +7046,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6950,16 +7351,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.42578125" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="92.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="101.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="75.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="94.42578125" customWidth="1"/>
-    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="84.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" style="1"/>
   </cols>
@@ -7025,10 +7427,10 @@
         <v>882</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J2" s="2">
-        <v>45967</v>
+        <v>45974</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -7036,174 +7438,174 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>142</v>
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>449</v>
+        <v>196</v>
+      </c>
+      <c r="E3" t="s">
+        <v>446</v>
       </c>
       <c r="F3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G3" t="s">
-        <v>451</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>880</v>
+        <v>448</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>882</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="J3" s="2">
-        <v>45979</v>
-      </c>
-      <c r="K3" s="1" t="s">
+        <v>45978</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F4" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="G4" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="J4" s="2">
-        <v>45980</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
+        <v>45979</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E5" t="s">
-        <v>452</v>
+        <v>145</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>443</v>
       </c>
       <c r="F5" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="G5" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="J5" s="2">
-        <v>45981</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
+        <v>45980</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="J6" s="2">
-        <v>45982</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
+        <v>45981</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>458</v>
+        <v>149</v>
+      </c>
+      <c r="E7" t="s">
+        <v>455</v>
       </c>
       <c r="F7" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="J7" s="2">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -7211,34 +7613,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" t="s">
-        <v>461</v>
+        <v>151</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>458</v>
       </c>
       <c r="F8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G8" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="J8" s="2">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -7246,34 +7648,34 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F9" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="J9" s="2">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -7281,34 +7683,34 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F10" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G10" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="J10" s="2">
-        <v>45988</v>
+        <v>45987</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -7316,28 +7718,34 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>473</v>
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" t="s">
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F11" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="J11" s="2">
-        <v>45989</v>
+        <v>45988</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -7345,34 +7753,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" t="s">
-        <v>159</v>
+        <v>473</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1042</v>
       </c>
       <c r="E12" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F12" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G12" t="s">
-        <v>476</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>900</v>
+        <v>472</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>897</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="J12" s="2">
-        <v>45992</v>
+        <v>45989</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -7380,34 +7788,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F13" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="G13" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="J13" s="2">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -7415,34 +7823,34 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="G14" t="s">
-        <v>482</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>903</v>
+        <v>479</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>900</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J14" s="2">
-        <v>45994</v>
+        <v>45993</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -7450,34 +7858,34 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F15" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G15" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="J15" s="2">
-        <v>45995</v>
+        <v>45994</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -7485,34 +7893,34 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F16" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G16" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="J16" s="2">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -7520,34 +7928,34 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F17" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="G17" t="s">
-        <v>491</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>906</v>
+        <v>488</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>904</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J17" s="2">
-        <v>45999</v>
+        <v>45996</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -7555,34 +7963,34 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F18" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="G18" t="s">
-        <v>494</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>907</v>
+        <v>491</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>905</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="J18" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -7590,34 +7998,34 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F19" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="G19" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
       <c r="J19" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -7625,34 +8033,34 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F20" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="G20" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="J20" s="2">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -7660,34 +8068,34 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E21" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F21" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G21" t="s">
-        <v>503</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>912</v>
+        <v>500</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>910</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="J21" s="2">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -7695,34 +8103,34 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F22" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="G22" t="s">
-        <v>506</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>889</v>
+        <v>503</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>911</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="J22" s="2">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -7730,34 +8138,34 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F23" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="G23" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>914</v>
+        <v>889</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>902</v>
+        <v>888</v>
       </c>
       <c r="J23" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -7765,34 +8173,34 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E24" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F24" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="G24" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J24" s="2">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -7800,34 +8208,34 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F25" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G25" t="s">
-        <v>515</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>916</v>
+        <v>512</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>914</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J25" s="2">
-        <v>46009</v>
+        <v>46008</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -7835,34 +8243,34 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F26" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G26" t="s">
-        <v>518</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>917</v>
+        <v>515</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>915</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J26" s="2">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
@@ -7870,34 +8278,34 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E27" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F27" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G27" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>919</v>
+        <v>901</v>
       </c>
       <c r="J27" s="2">
-        <v>45968</v>
+        <v>46010</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -7905,34 +8313,34 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E28" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F28" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="G28" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>920</v>
+        <v>1049</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J28" s="2">
-        <v>46014</v>
+        <v>45968</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -7940,31 +8348,34 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>190</v>
+      </c>
+      <c r="D29" t="s">
+        <v>191</v>
       </c>
       <c r="E29" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F29" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G29" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J29" s="2">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
@@ -7972,28 +8383,34 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>1043</v>
       </c>
       <c r="E30" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F30" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G30" t="s">
-        <v>530</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>922</v>
+        <v>527</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J30" s="2">
-        <v>46016</v>
+        <v>46015</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -8001,31 +8418,34 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>197</v>
-      </c>
-      <c r="D31" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>1044</v>
       </c>
       <c r="E31" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F31" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G31" t="s">
-        <v>533</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>923</v>
+        <v>530</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>920</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J31" s="2">
-        <v>46017</v>
+        <v>46016</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -8033,28 +8453,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E32" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F32" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G32" t="s">
-        <v>536</v>
+        <v>533</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J32" s="2">
-        <v>46020</v>
+        <v>46017</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -8062,28 +8488,34 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F33" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G33" t="s">
-        <v>539</v>
+        <v>536</v>
+      </c>
+      <c r="H33" t="s">
+        <v>922</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J33" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -8091,28 +8523,34 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E34" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F34" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="G34" t="s">
-        <v>542</v>
+        <v>539</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J34" s="2">
-        <v>46022</v>
+        <v>46021</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -8120,28 +8558,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D35" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E35" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F35" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G35" t="s">
-        <v>545</v>
+        <v>542</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J35" s="2">
-        <v>46024</v>
+        <v>46022</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -8149,28 +8593,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E36" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F36" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="G36" t="s">
-        <v>548</v>
+        <v>545</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J36" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -8178,28 +8628,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E37" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F37" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="G37" t="s">
-        <v>551</v>
+        <v>548</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J37" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -8207,28 +8663,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D38" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E38" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F38" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="G38" t="s">
-        <v>554</v>
+        <v>551</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J38" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -8236,28 +8698,34 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E39" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F39" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G39" t="s">
-        <v>557</v>
+        <v>554</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>929</v>
       </c>
       <c r="J39" s="2">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -8265,28 +8733,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D40" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E40" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F40" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="G40" t="s">
-        <v>560</v>
+        <v>557</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>886</v>
       </c>
       <c r="J40" s="2">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
@@ -8294,28 +8768,34 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>217</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
+      </c>
+      <c r="D41" t="s">
+        <v>216</v>
       </c>
       <c r="E41" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="F41" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="G41" t="s">
-        <v>563</v>
+        <v>560</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>932</v>
       </c>
       <c r="J41" s="2">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
@@ -8323,28 +8803,34 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
-      </c>
-      <c r="D42" t="s">
-        <v>220</v>
+        <v>217</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="E42" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F42" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G42" t="s">
-        <v>566</v>
+        <v>563</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>933</v>
       </c>
       <c r="J42" s="2">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
@@ -8352,28 +8838,34 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E43" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F43" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G43" t="s">
-        <v>569</v>
+        <v>566</v>
+      </c>
+      <c r="H43" t="s">
+        <v>935</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>936</v>
       </c>
       <c r="J43" s="2">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="K43" s="1">
         <v>0</v>
@@ -8381,28 +8873,34 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D44" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E44" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F44" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="G44" t="s">
-        <v>572</v>
+        <v>569</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J44" s="2">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
@@ -8410,28 +8908,34 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E45" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F45" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G45" t="s">
-        <v>575</v>
+        <v>572</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J45" s="2">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
@@ -8439,28 +8943,34 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E46" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F46" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="G46" t="s">
-        <v>578</v>
+        <v>575</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J46" s="2">
-        <v>46055</v>
+        <v>46038</v>
       </c>
       <c r="K46" s="1">
         <v>0</v>
@@ -8468,28 +8978,34 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D47" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F47" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="G47" t="s">
-        <v>581</v>
+        <v>578</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>940</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J47" s="2">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -8497,28 +9013,34 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E48" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F48" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G48" t="s">
-        <v>586</v>
+        <v>581</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>942</v>
       </c>
       <c r="J48" s="2">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
@@ -8526,25 +9048,34 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D49" t="s">
-        <v>234</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>582</v>
+        <v>232</v>
+      </c>
+      <c r="E49" t="s">
+        <v>584</v>
       </c>
       <c r="F49" t="s">
-        <v>583</v>
+        <v>585</v>
+      </c>
+      <c r="G49" t="s">
+        <v>586</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J49" s="2">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
@@ -8552,28 +9083,31 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D50" t="s">
-        <v>236</v>
-      </c>
-      <c r="E50" t="s">
-        <v>587</v>
+        <v>234</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>582</v>
       </c>
       <c r="F50" t="s">
-        <v>588</v>
-      </c>
-      <c r="G50" t="s">
-        <v>589</v>
+        <v>583</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J50" s="2">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
@@ -8581,28 +9115,34 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E51" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F51" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G51" t="s">
-        <v>592</v>
+        <v>589</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>946</v>
       </c>
       <c r="J51" s="2">
-        <v>46062</v>
+        <v>46059</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
@@ -8610,28 +9150,34 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D52" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E52" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F52" t="s">
-        <v>878</v>
+        <v>591</v>
       </c>
       <c r="G52" t="s">
-        <v>879</v>
+        <v>592</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J52" s="2">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="K52" s="1">
         <v>0</v>
@@ -8639,28 +9185,34 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D53" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E53" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F53" t="s">
-        <v>599</v>
+        <v>878</v>
       </c>
       <c r="G53" t="s">
-        <v>599</v>
+        <v>879</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J53" s="2">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -8668,28 +9220,34 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E54" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F54" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G54" t="s">
-        <v>601</v>
+        <v>599</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J54" s="2">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -8697,28 +9255,34 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D55" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E55" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F55" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G55" t="s">
-        <v>603</v>
+        <v>601</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J55" s="2">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="K55" s="1">
         <v>0</v>
@@ -8726,28 +9290,34 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D56" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E56" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G56" t="s">
-        <v>605</v>
+        <v>603</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>917</v>
       </c>
       <c r="J56" s="2">
-        <v>46069</v>
+        <v>46066</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
@@ -8755,28 +9325,34 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D57" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E57" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F57" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G57" t="s">
-        <v>607</v>
+        <v>605</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J57" s="2">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
@@ -8784,28 +9360,34 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E58" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="F58" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G58" t="s">
-        <v>610</v>
+        <v>607</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J58" s="2">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -8813,28 +9395,34 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D59" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E59" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F59" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="G59" t="s">
-        <v>613</v>
+        <v>610</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J59" s="2">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
@@ -8842,28 +9430,34 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D60" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E60" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F60" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="G60" t="s">
-        <v>616</v>
+        <v>613</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>955</v>
       </c>
       <c r="J60" s="2">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
@@ -8871,28 +9465,34 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D61" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E61" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F61" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="G61" t="s">
-        <v>619</v>
+        <v>616</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>936</v>
       </c>
       <c r="J61" s="2">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
@@ -8900,28 +9500,34 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>263</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D62" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E62" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F62" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="G62" t="s">
-        <v>622</v>
+        <v>619</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>958</v>
       </c>
       <c r="J62" s="2">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -8929,28 +9535,34 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="C63" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D63" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E63" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F63" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="G63" t="s">
-        <v>625</v>
+        <v>622</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>960</v>
       </c>
       <c r="J63" s="2">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
@@ -8958,28 +9570,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E64" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F64" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="G64" t="s">
-        <v>628</v>
+        <v>625</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J64" s="2">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
@@ -8987,28 +9605,34 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D65" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E65" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F65" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="G65" t="s">
-        <v>631</v>
+        <v>628</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J65" s="2">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
@@ -9016,28 +9640,34 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D66" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E66" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F66" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G66" t="s">
-        <v>634</v>
+        <v>631</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J66" s="2">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -9045,28 +9675,34 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D67" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E67" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F67" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G67" t="s">
-        <v>637</v>
+        <v>634</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J67" s="2">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
@@ -9074,28 +9710,34 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D68" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E68" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F68" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="G68" t="s">
-        <v>640</v>
+        <v>637</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J68" s="2">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
@@ -9103,28 +9745,34 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E69" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F69" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G69" t="s">
-        <v>643</v>
+        <v>640</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>967</v>
       </c>
       <c r="J69" s="2">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -9132,28 +9780,34 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D70" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E70" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F70" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="G70" t="s">
-        <v>646</v>
+        <v>643</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J70" s="2">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
@@ -9161,28 +9815,34 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D71" t="s">
-        <v>283</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>647</v>
+        <v>281</v>
+      </c>
+      <c r="E71" t="s">
+        <v>644</v>
       </c>
       <c r="F71" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="G71" t="s">
-        <v>649</v>
+        <v>646</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J71" s="2">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
@@ -9190,28 +9850,34 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D72" t="s">
-        <v>286</v>
-      </c>
-      <c r="E72" t="s">
-        <v>650</v>
+        <v>283</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>647</v>
       </c>
       <c r="F72" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G72" t="s">
-        <v>652</v>
+        <v>649</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J72" s="2">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
@@ -9219,28 +9885,34 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="C73" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D73" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E73" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F73" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G73" t="s">
-        <v>655</v>
+        <v>652</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J73" s="2">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
@@ -9248,28 +9920,34 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="D74" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="E74" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F74" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G74" t="s">
-        <v>658</v>
+        <v>655</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="J74" s="2">
-        <v>46093</v>
+        <v>46092</v>
       </c>
       <c r="K74" s="1">
         <v>0</v>
@@ -9277,28 +9955,34 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C75" t="s">
-        <v>289</v>
+        <v>192</v>
       </c>
       <c r="D75" t="s">
-        <v>290</v>
+        <v>193</v>
       </c>
       <c r="E75" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F75" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G75" t="s">
-        <v>661</v>
+        <v>658</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>895</v>
       </c>
       <c r="J75" s="2">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
@@ -9306,28 +9990,34 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D76" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E76" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F76" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G76" t="s">
-        <v>664</v>
+        <v>661</v>
+      </c>
+      <c r="H76" t="s">
+        <v>973</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="J76" s="2">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="K76" s="1">
         <v>0</v>
@@ -9335,28 +10025,34 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D77" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E77" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="F77" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="G77" t="s">
-        <v>667</v>
+        <v>664</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J77" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="K77" s="1">
         <v>0</v>
@@ -9364,28 +10060,34 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>259</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D78" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E78" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F78" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="G78" t="s">
-        <v>670</v>
+        <v>667</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J78" s="2">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="K78" s="1">
         <v>0</v>
@@ -9393,28 +10095,34 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>259</v>
       </c>
       <c r="C79" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D79" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E79" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F79" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G79" t="s">
-        <v>673</v>
+        <v>670</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>886</v>
       </c>
       <c r="J79" s="2">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="K79" s="1">
         <v>0</v>
@@ -9422,28 +10130,34 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D80" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E80" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F80" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="G80" t="s">
-        <v>676</v>
+        <v>673</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>976</v>
       </c>
       <c r="J80" s="2">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
@@ -9451,28 +10165,34 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D81" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E81" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F81" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="G81" t="s">
-        <v>679</v>
+        <v>676</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>946</v>
       </c>
       <c r="J81" s="2">
-        <v>46104</v>
+        <v>46101</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
@@ -9480,28 +10200,34 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D82" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E82" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F82" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G82" t="s">
-        <v>682</v>
+        <v>679</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J82" s="2">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="K82" s="1">
         <v>0</v>
@@ -9509,28 +10235,34 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C83" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D83" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E83" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="F83" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G83" t="s">
-        <v>685</v>
+        <v>682</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J83" s="2">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="K83" s="1">
         <v>0</v>
@@ -9538,28 +10270,34 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C84" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D84" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E84" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="F84" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="G84" t="s">
-        <v>688</v>
+        <v>685</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J84" s="2">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
@@ -9567,28 +10305,34 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C85" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D85" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E85" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F85" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G85" t="s">
-        <v>691</v>
+        <v>688</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J85" s="2">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
@@ -9596,28 +10340,34 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D86" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E86" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F86" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="G86" t="s">
-        <v>694</v>
+        <v>691</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J86" s="2">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="K86" s="1">
         <v>0</v>
@@ -9625,25 +10375,34 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>258</v>
+        <v>92</v>
       </c>
       <c r="C87" t="s">
-        <v>313</v>
+        <v>311</v>
+      </c>
+      <c r="D87" t="s">
+        <v>312</v>
       </c>
       <c r="E87" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F87" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G87" t="s">
-        <v>697</v>
+        <v>694</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J87" s="2">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="K87" s="1">
         <v>0</v>
@@ -9651,28 +10410,34 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>258</v>
       </c>
       <c r="C88" t="s">
-        <v>314</v>
-      </c>
-      <c r="D88" t="s">
-        <v>315</v>
+        <v>313</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>1045</v>
       </c>
       <c r="E88" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F88" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="G88" t="s">
-        <v>700</v>
+        <v>697</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J88" s="2">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="K88" s="1">
         <v>0</v>
@@ -9680,28 +10445,34 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>316</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D89" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E89" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F89" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="G89" t="s">
-        <v>703</v>
+        <v>700</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J89" s="2">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="K89" s="1">
         <v>0</v>
@@ -9709,28 +10480,34 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>316</v>
       </c>
       <c r="C90" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D90" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E90" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F90" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G90" t="s">
-        <v>706</v>
+        <v>703</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J90" s="2">
-        <v>46115</v>
+        <v>46114</v>
       </c>
       <c r="K90" s="1">
         <v>0</v>
@@ -9738,28 +10515,34 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>321</v>
+        <v>94</v>
       </c>
       <c r="C91" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D91" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E91" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F91" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="G91" t="s">
-        <v>709</v>
+        <v>706</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J91" s="2">
-        <v>46118</v>
+        <v>46115</v>
       </c>
       <c r="K91" s="1">
         <v>0</v>
@@ -9767,28 +10550,34 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="C92" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D92" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E92" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F92" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="G92" t="s">
-        <v>712</v>
+        <v>709</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>988</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J92" s="2">
-        <v>46119</v>
+        <v>46118</v>
       </c>
       <c r="K92" s="1">
         <v>0</v>
@@ -9796,28 +10585,34 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C93" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D93" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E93" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F93" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="G93" t="s">
-        <v>715</v>
+        <v>712</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J93" s="2">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="K93" s="1">
         <v>0</v>
@@ -9825,28 +10620,34 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C94" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D94" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E94" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F94" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G94" t="s">
-        <v>718</v>
+        <v>715</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J94" s="2">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="K94" s="1">
         <v>0</v>
@@ -9854,28 +10655,34 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C95" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D95" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E95" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F95" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="G95" t="s">
-        <v>721</v>
+        <v>718</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J95" s="2">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="K95" s="1">
         <v>0</v>
@@ -9883,28 +10690,34 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C96" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D96" t="s">
-        <v>333</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>727</v>
+        <v>331</v>
+      </c>
+      <c r="E96" t="s">
+        <v>719</v>
+      </c>
+      <c r="F96" t="s">
+        <v>720</v>
+      </c>
+      <c r="G96" t="s">
+        <v>721</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J96" s="2">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="K96" s="1">
         <v>0</v>
@@ -9912,28 +10725,34 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C97" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D97" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>726</v>
+        <v>727</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J97" s="2">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="K97" s="1">
         <v>0</v>
@@ -9941,28 +10760,34 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D98" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>730</v>
+        <v>726</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J98" s="2">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="K98" s="1">
         <v>0</v>
@@ -9970,28 +10795,34 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C99" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D99" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>733</v>
+        <v>730</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J99" s="2">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="K99" s="1">
         <v>0</v>
@@ -9999,28 +10830,34 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C100" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D100" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>736</v>
+        <v>733</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J100" s="2">
-        <v>46129</v>
+        <v>46128</v>
       </c>
       <c r="K100" s="1">
         <v>0</v>
@@ -10028,28 +10865,34 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C101" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D101" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J101" s="2">
-        <v>46132</v>
+        <v>46129</v>
       </c>
       <c r="K101" s="1">
         <v>0</v>
@@ -10057,28 +10900,34 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C102" t="s">
-        <v>344</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
+      </c>
+      <c r="D102" t="s">
+        <v>343</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>742</v>
+        <v>739</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J102" s="2">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="K102" s="1">
         <v>0</v>
@@ -10086,28 +10935,34 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>346</v>
+        <v>105</v>
       </c>
       <c r="C103" t="s">
-        <v>347</v>
-      </c>
-      <c r="D103" t="s">
-        <v>348</v>
+        <v>344</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>745</v>
+        <v>742</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J103" s="2">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="K103" s="1">
         <v>0</v>
@@ -10115,28 +10970,34 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>106</v>
+        <v>346</v>
       </c>
       <c r="C104" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D104" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>748</v>
+        <v>745</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J104" s="2">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="K104" s="1">
         <v>0</v>
@@ -10144,28 +11005,34 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D105" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>751</v>
+        <v>748</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J105" s="2">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="K105" s="1">
         <v>0</v>
@@ -10173,28 +11040,34 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="C106" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>754</v>
+        <v>751</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J106" s="2">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="K106" s="1">
         <v>0</v>
@@ -10202,28 +11075,34 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="C107" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>757</v>
+        <v>754</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J107" s="2">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="K107" s="1">
         <v>0</v>
@@ -10231,28 +11110,34 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108" t="s">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
-        <v>108</v>
-      </c>
       <c r="C108" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>760</v>
+        <v>757</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J108" s="2">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="K108" s="1">
         <v>0</v>
@@ -10260,28 +11145,34 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109" t="s">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
-        <v>109</v>
-      </c>
       <c r="C109" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>763</v>
+        <v>760</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J109" s="2">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="K109" s="1">
         <v>0</v>
@@ -10289,28 +11180,34 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110" t="s">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
-        <v>110</v>
-      </c>
       <c r="C110" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>766</v>
+        <v>763</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J110" s="2">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="K110" s="1">
         <v>0</v>
@@ -10318,28 +11215,34 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111" t="s">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
-        <v>111</v>
-      </c>
       <c r="C111" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>769</v>
+        <v>766</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J111" s="2">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="K111" s="1">
         <v>0</v>
@@ -10347,28 +11250,34 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112" t="s">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
-        <v>112</v>
-      </c>
       <c r="C112" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>772</v>
+        <v>769</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J112" s="2">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="K112" s="1">
         <v>0</v>
@@ -10376,28 +11285,34 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113" t="s">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
-        <v>367</v>
-      </c>
       <c r="C113" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D113" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>775</v>
+        <v>772</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J113" s="2">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="K113" s="1">
         <v>0</v>
@@ -10405,28 +11320,34 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C114" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D114" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>778</v>
+        <v>775</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J114" s="2">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="K114" s="1">
         <v>0</v>
@@ -10434,28 +11355,34 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>370</v>
       </c>
       <c r="C115" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D115" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>781</v>
+        <v>778</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J115" s="2">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="K115" s="1">
         <v>0</v>
@@ -10463,28 +11390,34 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>260</v>
+        <v>113</v>
       </c>
       <c r="C116" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D116" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>784</v>
+        <v>781</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J116" s="2">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="K116" s="1">
         <v>0</v>
@@ -10492,28 +11425,34 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="C117" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>787</v>
+        <v>784</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J117" s="2">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="K117" s="1">
         <v>0</v>
@@ -10521,28 +11460,34 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>379</v>
+        <v>114</v>
       </c>
       <c r="C118" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>790</v>
+        <v>787</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J118" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="K118" s="1">
         <v>0</v>
@@ -10550,28 +11495,34 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>139</v>
+        <v>379</v>
       </c>
       <c r="C119" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>792</v>
-      </c>
-      <c r="G119" t="s">
-        <v>793</v>
+        <v>789</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J119" s="2">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="K119" s="1">
         <v>0</v>
@@ -10579,28 +11530,34 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>384</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>386</v>
+        <v>139</v>
+      </c>
+      <c r="C120" t="s">
+        <v>382</v>
+      </c>
+      <c r="D120" t="s">
+        <v>383</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>796</v>
+        <v>792</v>
+      </c>
+      <c r="G120" t="s">
+        <v>793</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J120" s="2">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="K120" s="1">
         <v>0</v>
@@ -10608,28 +11565,34 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
-      </c>
-      <c r="C121" t="s">
-        <v>387</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>388</v>
+        <v>384</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>386</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="G121" t="s">
-        <v>799</v>
+        <v>795</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J121" s="2">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="K121" s="1">
         <v>0</v>
@@ -10637,28 +11600,34 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C122" t="s">
-        <v>389</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E122" t="s">
-        <v>800</v>
-      </c>
-      <c r="F122" t="s">
-        <v>801</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>802</v>
+        <v>387</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="G122" t="s">
+        <v>799</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J122" s="2">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="K122" s="1">
         <v>0</v>
@@ -10666,28 +11635,34 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C123" t="s">
-        <v>391</v>
-      </c>
-      <c r="D123" t="s">
-        <v>392</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="F123" s="8" t="s">
-        <v>804</v>
-      </c>
-      <c r="G123" t="s">
-        <v>805</v>
+        <v>389</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E123" t="s">
+        <v>800</v>
+      </c>
+      <c r="F123" t="s">
+        <v>801</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="H123" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J123" s="2">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="K123" s="1">
         <v>0</v>
@@ -10695,28 +11670,34 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C124" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D124" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>806</v>
-      </c>
-      <c r="F124" t="s">
-        <v>807</v>
-      </c>
-      <c r="G124" s="9" t="s">
-        <v>808</v>
+        <v>803</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="G124" t="s">
+        <v>805</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J124" s="2">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="K124" s="1">
         <v>0</v>
@@ -10724,28 +11705,34 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C125" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D125" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="G125" t="s">
-        <v>811</v>
+        <v>806</v>
+      </c>
+      <c r="F125" t="s">
+        <v>807</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>808</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J125" s="2">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="K125" s="1">
         <v>0</v>
@@ -10753,28 +11740,34 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C126" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D126" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="F126" t="s">
-        <v>813</v>
+        <v>809</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>810</v>
       </c>
       <c r="G126" t="s">
-        <v>814</v>
+        <v>811</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J126" s="2">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="K126" s="1">
         <v>0</v>
@@ -10782,28 +11775,34 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C127" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D127" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="F127" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="G127" t="s">
-        <v>817</v>
+        <v>814</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J127" s="2">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="K127" s="1">
         <v>0</v>
@@ -10811,28 +11810,34 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C128" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D128" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="F128" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="G128" t="s">
-        <v>820</v>
+        <v>817</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J128" s="2">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="K128" s="1">
         <v>0</v>
@@ -10840,28 +11845,34 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C129" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D129" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F129" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="G129" t="s">
-        <v>823</v>
+        <v>820</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J129" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="K129" s="1">
         <v>0</v>
@@ -10869,28 +11880,34 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C130" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D130" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F130" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G130" t="s">
-        <v>826</v>
+        <v>823</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J130" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="K130" s="1">
         <v>0</v>
@@ -10898,28 +11915,34 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C131" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D131" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="F131" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="G131" t="s">
-        <v>829</v>
+        <v>826</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J131" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="K131" s="1">
         <v>0</v>
@@ -10927,28 +11950,34 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C132" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D132" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="F132" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="G132" t="s">
-        <v>832</v>
+        <v>829</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J132" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="K132" s="1">
         <v>0</v>
@@ -10956,28 +11985,34 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>412</v>
+        <v>127</v>
       </c>
       <c r="C133" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D133" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="F133" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="G133" t="s">
-        <v>835</v>
+        <v>832</v>
+      </c>
+      <c r="H133" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J133" s="2">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="K133" s="1">
         <v>0</v>
@@ -10985,28 +12020,34 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>128</v>
+        <v>412</v>
       </c>
       <c r="C134" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D134" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="F134" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="G134" t="s">
-        <v>838</v>
+        <v>835</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J134" s="2">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="K134" s="1">
         <v>0</v>
@@ -11014,28 +12055,34 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C135" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D135" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="F135" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="G135" t="s">
-        <v>841</v>
+        <v>838</v>
+      </c>
+      <c r="H135" s="8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J135" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="K135" s="1">
         <v>0</v>
@@ -11043,28 +12090,34 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C136" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D136" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="F136" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="G136" t="s">
-        <v>844</v>
+        <v>841</v>
+      </c>
+      <c r="H136" s="8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J136" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="K136" s="1">
         <v>0</v>
@@ -11072,28 +12125,34 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C137" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D137" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="F137" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="G137" t="s">
-        <v>847</v>
+        <v>844</v>
+      </c>
+      <c r="H137" s="8" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I137" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J137" s="2">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="K137" s="1">
         <v>0</v>
@@ -11101,28 +12160,34 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>395</v>
+        <v>131</v>
       </c>
       <c r="C138" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D138" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="F138" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="G138" t="s">
-        <v>850</v>
+        <v>847</v>
+      </c>
+      <c r="H138" s="8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J138" s="2">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="K138" s="1">
         <v>0</v>
@@ -11130,28 +12195,34 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>132</v>
+        <v>395</v>
       </c>
       <c r="C139" t="s">
-        <v>425</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
+      </c>
+      <c r="D139" t="s">
+        <v>424</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="F139" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="G139" t="s">
-        <v>853</v>
+        <v>850</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J139" s="2">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="K139" s="1">
         <v>0</v>
@@ -11159,28 +12230,34 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C140" t="s">
-        <v>427</v>
-      </c>
-      <c r="D140" t="s">
-        <v>428</v>
+        <v>425</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="F140" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="G140" t="s">
-        <v>856</v>
+        <v>853</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J140" s="2">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="K140" s="1">
         <v>0</v>
@@ -11188,28 +12265,34 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C141" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D141" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="F141" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="G141" t="s">
-        <v>859</v>
+        <v>856</v>
+      </c>
+      <c r="H141" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I141" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J141" s="2">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="K141" s="1">
         <v>0</v>
@@ -11217,28 +12300,34 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C142" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D142" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F142" t="s">
-        <v>861</v>
-      </c>
-      <c r="G142" s="9" t="s">
-        <v>862</v>
+        <v>858</v>
+      </c>
+      <c r="G142" t="s">
+        <v>859</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I142" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J142" s="2">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="K142" s="1">
         <v>0</v>
@@ -11246,28 +12335,34 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C143" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D143" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="F143" t="s">
-        <v>864</v>
-      </c>
-      <c r="G143" t="s">
-        <v>865</v>
+        <v>861</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H143" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J143" s="2">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="K143" s="1">
         <v>0</v>
@@ -11275,28 +12370,34 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C144" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D144" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="F144" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="G144" t="s">
-        <v>868</v>
+        <v>865</v>
+      </c>
+      <c r="H144" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I144" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J144" s="2">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="K144" s="1">
         <v>0</v>
@@ -11304,28 +12405,34 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C145" t="s">
-        <v>437</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
+      </c>
+      <c r="D145" t="s">
+        <v>436</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F145" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="G145" t="s">
-        <v>871</v>
+        <v>868</v>
+      </c>
+      <c r="H145" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I145" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J145" s="2">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="K145" s="1">
         <v>0</v>
@@ -11333,28 +12440,34 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C146" t="s">
-        <v>439</v>
-      </c>
-      <c r="D146" t="s">
-        <v>440</v>
+        <v>437</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>438</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="F146" t="s">
-        <v>873</v>
-      </c>
-      <c r="G146" s="9" t="s">
-        <v>874</v>
+        <v>870</v>
+      </c>
+      <c r="G146" t="s">
+        <v>871</v>
+      </c>
+      <c r="H146" s="8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I146" s="8" t="s">
+        <v>901</v>
       </c>
       <c r="J146" s="2">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="K146" s="1">
         <v>0</v>
@@ -11362,32 +12475,76 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147" t="s">
+        <v>115</v>
+      </c>
+      <c r="C147" t="s">
+        <v>439</v>
+      </c>
+      <c r="D147" t="s">
+        <v>440</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="F147" t="s">
+        <v>873</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="H147" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I147" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="J147" s="2">
+        <v>46198</v>
+      </c>
+      <c r="K147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A148">
         <v>146</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B148" t="s">
         <v>140</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C148" t="s">
         <v>441</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D148" t="s">
         <v>442</v>
       </c>
-      <c r="E147" s="8" t="s">
+      <c r="E148" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F148" t="s">
         <v>876</v>
       </c>
-      <c r="G147" t="s">
+      <c r="G148" t="s">
         <v>877</v>
       </c>
-      <c r="J147" s="2">
+      <c r="H148" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I148" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="J148" s="2">
         <v>46199</v>
       </c>
-      <c r="K147" s="1">
-        <v>0</v>
-      </c>
+      <c r="K148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H153" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
+++ b/DILIMIZINZENGINLIKLERI2/bin/Debug/KELIMELER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr backupFile="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CENGİZ\Desktop\EVOKUL\DILIMIZINZENGINLIKLERI2\bin\Debug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CENGİZ\Desktop\OKULEV\DILIMIZINZENGINLIKLERI2\bin\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07041174-0D36-4726-8B9E-3904FAE1391E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC58F907-A963-4617-9042-A8BA6E5DD673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7439,7 +7439,7 @@
         <v>908</v>
       </c>
       <c r="J2" s="2">
-        <v>45978</v>
+        <v>45974</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
